--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-01.xlsx
@@ -766,7 +766,7 @@
     <t>Sport Boys (Per)</t>
   </si>
   <si>
-    <t>2026-07-30 00:42:57</t>
+    <t>2026-07-30 02:52:20</t>
   </si>
 </sst>
 </file>
@@ -1360,13 +1360,13 @@
         <v>191</v>
       </c>
       <c r="F2">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="G2">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="H2">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="I2">
         <v>2.94</v>
@@ -1378,61 +1378,61 @@
         <v>3.65</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M2">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
         <v>3.55</v>
       </c>
       <c r="O2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q2">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="R2">
         <v>1.3</v>
       </c>
       <c r="S2">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T2">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="U2">
-        <v>1.79</v>
+        <v>2.14</v>
       </c>
       <c r="V2">
         <v>1.51</v>
       </c>
       <c r="W2">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X2">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z2">
         <v>28</v>
       </c>
       <c r="AA2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC2">
         <v>11</v>
       </c>
       <c r="AD2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE2">
         <v>46</v>
@@ -1441,19 +1441,19 @@
         <v>25</v>
       </c>
       <c r="AG2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI2">
         <v>60</v>
       </c>
       <c r="AJ2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL2">
         <v>55</v>
@@ -1468,76 +1468,76 @@
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>10</v>
+        <v>2.28</v>
       </c>
       <c r="AQ2">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AR2">
         <v>13.5</v>
       </c>
       <c r="AS2">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="AT2">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="AU2">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="AV2">
         <v>9.4</v>
       </c>
       <c r="AW2">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="AX2">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="AY2">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AZ2">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="BA2">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="BB2">
-        <v>2.48</v>
+        <v>2.18</v>
       </c>
       <c r="BC2">
-        <v>2.44</v>
+        <v>20</v>
       </c>
       <c r="BD2">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="BE2">
-        <v>2.58</v>
+        <v>2.28</v>
       </c>
       <c r="BF2">
-        <v>2.58</v>
+        <v>2.28</v>
       </c>
       <c r="BG2">
-        <v>2.58</v>
+        <v>2.28</v>
       </c>
       <c r="BH2">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.7</v>
+        <v>1.89</v>
       </c>
       <c r="BJ2">
         <v>13</v>
       </c>
       <c r="BK2">
-        <v>2.9</v>
+        <v>1.65</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>3.7</v>
+        <v>1.89</v>
       </c>
       <c r="BN2">
         <v>7.8</v>
@@ -1546,16 +1546,16 @@
         <v>3.9</v>
       </c>
       <c r="BP2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BQ2">
-        <v>3.3</v>
+        <v>1.77</v>
       </c>
       <c r="BR2">
         <v>48</v>
       </c>
       <c r="BS2">
-        <v>3.45</v>
+        <v>1.82</v>
       </c>
       <c r="BT2">
         <v>7.8</v>
@@ -1564,22 +1564,22 @@
         <v>3.9</v>
       </c>
       <c r="BV2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW2">
-        <v>3.3</v>
+        <v>1.77</v>
       </c>
       <c r="BX2">
         <v>48</v>
       </c>
       <c r="BY2">
-        <v>3.45</v>
+        <v>1.82</v>
       </c>
       <c r="BZ2">
         <v>38</v>
       </c>
       <c r="CA2">
-        <v>3.35</v>
+        <v>1.8</v>
       </c>
       <c r="CB2" t="s">
         <v>250</v>
@@ -1620,7 +1620,7 @@
         <v>3.5</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M3">
         <v>1.01</v>
@@ -1844,7 +1844,7 @@
         <v>193</v>
       </c>
       <c r="F4">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="G4">
         <v>1.62</v>
@@ -1859,7 +1859,7 @@
         <v>3.95</v>
       </c>
       <c r="K4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1868,22 +1868,22 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P4">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Q4">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="R4">
         <v>1.13</v>
       </c>
       <c r="S4">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1910,7 +1910,7 @@
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4">
         <v>1000</v>
@@ -1928,13 +1928,13 @@
         <v>1000</v>
       </c>
       <c r="AH4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI4">
         <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
         <v>1000</v>
@@ -1952,58 +1952,58 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AQ4">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AR4">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AS4">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AT4">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AU4">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AV4">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AW4">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AX4">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AY4">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AZ4">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="BA4">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="BB4">
-        <v>10</v>
+        <v>1.22</v>
       </c>
       <c r="BC4">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="BD4">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="BE4">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="BF4">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="BG4">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -2089,7 +2089,7 @@
         <v>5</v>
       </c>
       <c r="G5">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H5">
         <v>1.7</v>
@@ -2098,13 +2098,13 @@
         <v>1.78</v>
       </c>
       <c r="J5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M5">
         <v>1.05</v>
@@ -2119,28 +2119,28 @@
         <v>2.16</v>
       </c>
       <c r="Q5">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="R5">
         <v>1.46</v>
       </c>
       <c r="S5">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T5">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U5">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V5">
         <v>2.28</v>
       </c>
       <c r="W5">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X5">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="Y5">
         <v>11.5</v>
@@ -2149,7 +2149,7 @@
         <v>13</v>
       </c>
       <c r="AA5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB5">
         <v>24</v>
@@ -2158,13 +2158,13 @@
         <v>11.5</v>
       </c>
       <c r="AD5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AG5">
         <v>24</v>
@@ -2182,19 +2182,19 @@
         <v>75</v>
       </c>
       <c r="AL5">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM5">
         <v>110</v>
       </c>
       <c r="AN5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AP5">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ5">
         <v>8.800000000000001</v>
@@ -2206,7 +2206,7 @@
         <v>15.5</v>
       </c>
       <c r="AT5">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AU5">
         <v>8.6</v>
@@ -2218,46 +2218,46 @@
         <v>15</v>
       </c>
       <c r="AX5">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AY5">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AZ5">
         <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BB5">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BC5">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BD5">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BE5">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF5">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BG5">
         <v>7</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ5">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -2266,7 +2266,7 @@
         <v>21</v>
       </c>
       <c r="BN5">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO5">
         <v>5.8</v>
@@ -2278,34 +2278,34 @@
         <v>21</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS5">
         <v>21</v>
       </c>
       <c r="BT5">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BU5">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="BV5">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BW5">
         <v>7.2</v>
       </c>
       <c r="BX5">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BY5">
         <v>15</v>
       </c>
       <c r="BZ5">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="CA5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CB5" t="s">
         <v>250</v>
@@ -2328,19 +2328,19 @@
         <v>195</v>
       </c>
       <c r="F6">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G6">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="H6">
+        <v>3.6</v>
+      </c>
+      <c r="I6">
+        <v>4.2</v>
+      </c>
+      <c r="J6">
         <v>3.55</v>
-      </c>
-      <c r="I6">
-        <v>4.1</v>
-      </c>
-      <c r="J6">
-        <v>3.35</v>
       </c>
       <c r="K6">
         <v>3.95</v>
@@ -2349,91 +2349,91 @@
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N6">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="O6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P6">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q6">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="R6">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="S6">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V6">
         <v>1.32</v>
       </c>
       <c r="W6">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP6">
         <v>1.03</v>
@@ -2442,13 +2442,13 @@
         <v>1.03</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AS6">
         <v>1.03</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AU6">
         <v>1.03</v>
@@ -2472,10 +2472,10 @@
         <v>1.03</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BD6">
         <v>1.03</v>
@@ -2484,10 +2484,10 @@
         <v>1.03</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BH6">
         <v>4.2</v>
@@ -2570,112 +2570,112 @@
         <v>196</v>
       </c>
       <c r="F7">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="G7">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="H7">
+        <v>2.28</v>
+      </c>
+      <c r="I7">
+        <v>2.54</v>
+      </c>
+      <c r="J7">
+        <v>3.2</v>
+      </c>
+      <c r="K7">
+        <v>4</v>
+      </c>
+      <c r="L7">
+        <v>1.27</v>
+      </c>
+      <c r="M7">
+        <v>1.05</v>
+      </c>
+      <c r="N7">
+        <v>4.2</v>
+      </c>
+      <c r="O7">
+        <v>1.23</v>
+      </c>
+      <c r="P7">
         <v>2.18</v>
       </c>
-      <c r="I7">
-        <v>2.9</v>
-      </c>
-      <c r="J7">
-        <v>3.25</v>
-      </c>
-      <c r="K7">
-        <v>5.2</v>
-      </c>
-      <c r="L7">
-        <v>1.01</v>
-      </c>
-      <c r="M7">
-        <v>1.01</v>
-      </c>
-      <c r="N7">
-        <v>2.2</v>
-      </c>
-      <c r="O7">
-        <v>1.17</v>
-      </c>
-      <c r="P7">
-        <v>2.2</v>
-      </c>
       <c r="Q7">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="R7">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S7">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="V7">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="W7">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AP7">
         <v>1.03</v>
@@ -2726,22 +2726,22 @@
         <v>1.03</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2750,46 +2750,46 @@
         <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="CB7" t="s">
         <v>250</v>
@@ -2815,163 +2815,163 @@
         <v>2.44</v>
       </c>
       <c r="G8">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H8">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="I8">
         <v>3.1</v>
       </c>
       <c r="J8">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K8">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L8">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N8">
         <v>4.5</v>
       </c>
       <c r="O8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P8">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q8">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R8">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="S8">
-        <v>1.74</v>
+        <v>2.84</v>
       </c>
       <c r="T8">
         <v>1.62</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="V8">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W8">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y8">
+        <v>15</v>
+      </c>
+      <c r="Z8">
+        <v>27</v>
+      </c>
+      <c r="AA8">
+        <v>55</v>
+      </c>
+      <c r="AB8">
+        <v>13.5</v>
+      </c>
+      <c r="AC8">
+        <v>10.5</v>
+      </c>
+      <c r="AD8">
+        <v>13.5</v>
+      </c>
+      <c r="AE8">
+        <v>36</v>
+      </c>
+      <c r="AF8">
+        <v>18.5</v>
+      </c>
+      <c r="AG8">
+        <v>12</v>
+      </c>
+      <c r="AH8">
         <v>15.5</v>
       </c>
-      <c r="Z8">
+      <c r="AI8">
+        <v>44</v>
+      </c>
+      <c r="AJ8">
+        <v>40</v>
+      </c>
+      <c r="AK8">
+        <v>25</v>
+      </c>
+      <c r="AL8">
+        <v>40</v>
+      </c>
+      <c r="AM8">
+        <v>80</v>
+      </c>
+      <c r="AN8">
+        <v>19.5</v>
+      </c>
+      <c r="AO8">
         <v>23</v>
       </c>
-      <c r="AA8">
-        <v>48</v>
-      </c>
-      <c r="AB8">
-        <v>14</v>
-      </c>
-      <c r="AC8">
-        <v>1000</v>
-      </c>
-      <c r="AD8">
-        <v>14</v>
-      </c>
-      <c r="AE8">
-        <v>1000</v>
-      </c>
-      <c r="AF8">
-        <v>19</v>
-      </c>
-      <c r="AG8">
+      <c r="AP8">
+        <v>16.5</v>
+      </c>
+      <c r="AQ8">
+        <v>13</v>
+      </c>
+      <c r="AR8">
+        <v>5.6</v>
+      </c>
+      <c r="AS8">
+        <v>6.2</v>
+      </c>
+      <c r="AT8">
+        <v>11.5</v>
+      </c>
+      <c r="AU8">
+        <v>7.8</v>
+      </c>
+      <c r="AV8">
+        <v>11.5</v>
+      </c>
+      <c r="AW8">
+        <v>5.9</v>
+      </c>
+      <c r="AX8">
+        <v>5.1</v>
+      </c>
+      <c r="AY8">
+        <v>10.5</v>
+      </c>
+      <c r="AZ8">
+        <v>4.8</v>
+      </c>
+      <c r="BA8">
+        <v>6</v>
+      </c>
+      <c r="BB8">
+        <v>6</v>
+      </c>
+      <c r="BC8">
+        <v>5.5</v>
+      </c>
+      <c r="BD8">
+        <v>6</v>
+      </c>
+      <c r="BE8">
+        <v>6.4</v>
+      </c>
+      <c r="BF8">
         <v>12.5</v>
       </c>
-      <c r="AH8">
+      <c r="BG8">
         <v>16</v>
-      </c>
-      <c r="AI8">
-        <v>1000</v>
-      </c>
-      <c r="AJ8">
-        <v>1000</v>
-      </c>
-      <c r="AK8">
-        <v>26</v>
-      </c>
-      <c r="AL8">
-        <v>1000</v>
-      </c>
-      <c r="AM8">
-        <v>1000</v>
-      </c>
-      <c r="AN8">
-        <v>1000</v>
-      </c>
-      <c r="AO8">
-        <v>1000</v>
-      </c>
-      <c r="AP8">
-        <v>2.02</v>
-      </c>
-      <c r="AQ8">
-        <v>10</v>
-      </c>
-      <c r="AR8">
-        <v>1.85</v>
-      </c>
-      <c r="AS8">
-        <v>1.93</v>
-      </c>
-      <c r="AT8">
-        <v>1.76</v>
-      </c>
-      <c r="AU8">
-        <v>2.02</v>
-      </c>
-      <c r="AV8">
-        <v>1.76</v>
-      </c>
-      <c r="AW8">
-        <v>2.02</v>
-      </c>
-      <c r="AX8">
-        <v>1.82</v>
-      </c>
-      <c r="AY8">
-        <v>1.73</v>
-      </c>
-      <c r="AZ8">
-        <v>1.79</v>
-      </c>
-      <c r="BA8">
-        <v>2.02</v>
-      </c>
-      <c r="BB8">
-        <v>2.02</v>
-      </c>
-      <c r="BC8">
-        <v>1.87</v>
-      </c>
-      <c r="BD8">
-        <v>2.02</v>
-      </c>
-      <c r="BE8">
-        <v>2.02</v>
-      </c>
-      <c r="BF8">
-        <v>2.02</v>
-      </c>
-      <c r="BG8">
-        <v>2.02</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2998,7 +2998,7 @@
         <v>3.7</v>
       </c>
       <c r="BP8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BQ8">
         <v>10.5</v>
@@ -3007,7 +3007,7 @@
         <v>40</v>
       </c>
       <c r="BS8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BT8">
         <v>8.800000000000001</v>
@@ -3028,7 +3028,7 @@
         <v>17.5</v>
       </c>
       <c r="BZ8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CA8">
         <v>12</v>
@@ -3066,46 +3066,46 @@
         <v>2.88</v>
       </c>
       <c r="J9">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K9">
         <v>3.75</v>
       </c>
       <c r="L9">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N9">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O9">
         <v>1.28</v>
       </c>
       <c r="P9">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q9">
         <v>1.86</v>
       </c>
       <c r="R9">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S9">
-        <v>1.87</v>
+        <v>3.15</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V9">
         <v>1.53</v>
       </c>
       <c r="W9">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X9">
         <v>16.5</v>
@@ -3114,52 +3114,52 @@
         <v>13</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP9">
         <v>13.5</v>
@@ -3171,7 +3171,7 @@
         <v>17</v>
       </c>
       <c r="AS9">
-        <v>1.21</v>
+        <v>4.6</v>
       </c>
       <c r="AT9">
         <v>10</v>
@@ -3183,7 +3183,7 @@
         <v>10.5</v>
       </c>
       <c r="AW9">
-        <v>1.21</v>
+        <v>4.4</v>
       </c>
       <c r="AX9">
         <v>15</v>
@@ -3195,19 +3195,19 @@
         <v>13.5</v>
       </c>
       <c r="BA9">
-        <v>1.21</v>
+        <v>4.5</v>
       </c>
       <c r="BB9">
-        <v>1.21</v>
+        <v>4.5</v>
       </c>
       <c r="BC9">
-        <v>1.21</v>
+        <v>4.4</v>
       </c>
       <c r="BD9">
-        <v>1.21</v>
+        <v>4.5</v>
       </c>
       <c r="BE9">
-        <v>1.21</v>
+        <v>4.8</v>
       </c>
       <c r="BF9">
         <v>15.5</v>
@@ -3225,55 +3225,55 @@
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="CB9" t="s">
         <v>250</v>
@@ -3550,7 +3550,7 @@
         <v>3.05</v>
       </c>
       <c r="J11">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K11">
         <v>4.2</v>
@@ -3571,7 +3571,7 @@
         <v>2.26</v>
       </c>
       <c r="Q11">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3813,7 +3813,7 @@
         <v>2.24</v>
       </c>
       <c r="Q12">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -4028,7 +4028,7 @@
         <v>2.28</v>
       </c>
       <c r="H13">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I13">
         <v>3.6</v>
@@ -4055,7 +4055,7 @@
         <v>2.34</v>
       </c>
       <c r="Q13">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -4506,22 +4506,22 @@
         <v>204</v>
       </c>
       <c r="F15">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="G15">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="H15">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I15">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J15">
         <v>4.4</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>1.44</v>
       </c>
       <c r="H18">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I18">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="J18">
         <v>5.5</v>
@@ -5265,7 +5265,7 @@
         <v>2.88</v>
       </c>
       <c r="Q18">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5961,7 +5961,7 @@
         <v>2.46</v>
       </c>
       <c r="G21">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H21">
         <v>2.9</v>
@@ -5970,7 +5970,7 @@
         <v>3.2</v>
       </c>
       <c r="J21">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K21">
         <v>3.8</v>
@@ -6215,7 +6215,7 @@
         <v>3.8</v>
       </c>
       <c r="K22">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6233,7 +6233,7 @@
         <v>2.3</v>
       </c>
       <c r="Q22">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6684,22 +6684,22 @@
         <v>213</v>
       </c>
       <c r="F24">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="G24">
         <v>2.18</v>
       </c>
       <c r="H24">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="I24">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="J24">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="K24">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6717,7 +6717,7 @@
         <v>2.14</v>
       </c>
       <c r="Q24">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6926,22 +6926,22 @@
         <v>214</v>
       </c>
       <c r="F25">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G25">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="H25">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I25">
         <v>2.4</v>
       </c>
       <c r="J25">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K25">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6956,10 +6956,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="Q25">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -7664,7 +7664,7 @@
         <v>4</v>
       </c>
       <c r="J28">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K28">
         <v>3.8</v>
@@ -7903,7 +7903,7 @@
         <v>2.68</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J29">
         <v>3.65</v>
@@ -8139,16 +8139,16 @@
         <v>2.14</v>
       </c>
       <c r="G30">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H30">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I30">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J30">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K30">
         <v>3.45</v>
@@ -8169,7 +8169,7 @@
         <v>1.57</v>
       </c>
       <c r="Q30">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -8178,7 +8178,7 @@
         <v>0</v>
       </c>
       <c r="T30">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U30">
         <v>1.79</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="X30">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y30">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z30">
         <v>32</v>
@@ -8205,28 +8205,28 @@
         <v>8.4</v>
       </c>
       <c r="AC30">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD30">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE30">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF30">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG30">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH30">
         <v>26</v>
       </c>
       <c r="AI30">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ30">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK30">
         <v>36</v>
@@ -8238,13 +8238,13 @@
         <v>190</v>
       </c>
       <c r="AN30">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO30">
         <v>110</v>
       </c>
       <c r="AP30">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AQ30">
         <v>8.800000000000001</v>
@@ -8253,7 +8253,7 @@
         <v>21</v>
       </c>
       <c r="AS30">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AT30">
         <v>6.2</v>
@@ -8265,7 +8265,7 @@
         <v>13</v>
       </c>
       <c r="AW30">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX30">
         <v>10</v>
@@ -8277,25 +8277,25 @@
         <v>17</v>
       </c>
       <c r="BA30">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BB30">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BC30">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BD30">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE30">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF30">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BG30">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BH30">
         <v>0</v>
@@ -8620,7 +8620,7 @@
         <v>221</v>
       </c>
       <c r="F32">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="G32">
         <v>6.2</v>
@@ -8650,10 +8650,10 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="Q32">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -8862,19 +8862,19 @@
         <v>222</v>
       </c>
       <c r="F33">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="G33">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H33">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J33">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K33">
         <v>4.7</v>
@@ -8892,10 +8892,10 @@
         <v>0</v>
       </c>
       <c r="P33">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q33">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -9110,10 +9110,10 @@
         <v>4.6</v>
       </c>
       <c r="H34">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="I34">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J34">
         <v>3.7</v>
@@ -9134,7 +9134,7 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q34">
         <v>1.63</v>
@@ -9349,19 +9349,19 @@
         <v>1.69</v>
       </c>
       <c r="G35">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="H35">
         <v>5</v>
       </c>
       <c r="I35">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J35">
         <v>3.75</v>
       </c>
       <c r="K35">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -9376,10 +9376,10 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q35">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -9588,16 +9588,16 @@
         <v>225</v>
       </c>
       <c r="F36">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G36">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H36">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I36">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J36">
         <v>3</v>
@@ -9830,16 +9830,16 @@
         <v>226</v>
       </c>
       <c r="F37">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="G37">
         <v>1.28</v>
       </c>
       <c r="H37">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="I37">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J37">
         <v>6.2</v>
@@ -9851,7 +9851,7 @@
         <v>0</v>
       </c>
       <c r="M37">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -9860,7 +9860,7 @@
         <v>0</v>
       </c>
       <c r="P37">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q37">
         <v>1.7</v>
@@ -9890,13 +9890,13 @@
         <v>950</v>
       </c>
       <c r="Z37">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AA37">
         <v>1000</v>
       </c>
       <c r="AB37">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC37">
         <v>16.5</v>
@@ -9905,7 +9905,7 @@
         <v>950</v>
       </c>
       <c r="AE37">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF37">
         <v>7.4</v>
@@ -9917,7 +9917,7 @@
         <v>55</v>
       </c>
       <c r="AI37">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="AJ37">
         <v>10.5</v>
@@ -9929,7 +9929,7 @@
         <v>60</v>
       </c>
       <c r="AM37">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AN37">
         <v>5.6</v>
@@ -9938,37 +9938,37 @@
         <v>1000</v>
       </c>
       <c r="AP37">
-        <v>17</v>
+        <v>4.8</v>
       </c>
       <c r="AQ37">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AR37">
+        <v>5.9</v>
+      </c>
+      <c r="AS37">
         <v>6</v>
       </c>
-      <c r="AS37">
-        <v>6.2</v>
-      </c>
       <c r="AT37">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU37">
-        <v>13</v>
+        <v>4.4</v>
       </c>
       <c r="AV37">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AW37">
         <v>6</v>
       </c>
       <c r="AX37">
-        <v>5.9</v>
+        <v>3.3</v>
       </c>
       <c r="AY37">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="AZ37">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BA37">
         <v>6</v>
@@ -9977,19 +9977,19 @@
         <v>7.4</v>
       </c>
       <c r="BC37">
-        <v>13</v>
+        <v>4.6</v>
       </c>
       <c r="BD37">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BE37">
         <v>6</v>
       </c>
       <c r="BF37">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="BG37">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH37">
         <v>0</v>
@@ -10559,7 +10559,7 @@
         <v>6</v>
       </c>
       <c r="G40">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="H40">
         <v>1.51</v>
@@ -10586,10 +10586,10 @@
         <v>0</v>
       </c>
       <c r="P40">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q40">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -11040,16 +11040,16 @@
         <v>231</v>
       </c>
       <c r="F42">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G42">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H42">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I42">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J42">
         <v>3.45</v>
@@ -11070,7 +11070,7 @@
         <v>0</v>
       </c>
       <c r="P42">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q42">
         <v>1.87</v>
@@ -11288,7 +11288,7 @@
         <v>2.1</v>
       </c>
       <c r="H43">
-        <v>1.91</v>
+        <v>3.65</v>
       </c>
       <c r="I43">
         <v>7.8</v>
@@ -11297,7 +11297,7 @@
         <v>3.65</v>
       </c>
       <c r="K43">
-        <v>950</v>
+        <v>7.8</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -11524,22 +11524,22 @@
         <v>233</v>
       </c>
       <c r="F44">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="G44">
-        <v>600</v>
+        <v>2.74</v>
       </c>
       <c r="H44">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="I44">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="J44">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="K44">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -11554,10 +11554,10 @@
         <v>0</v>
       </c>
       <c r="P44">
-        <v>1.25</v>
+        <v>1.88</v>
       </c>
       <c r="Q44">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -11769,7 +11769,7 @@
         <v>3.15</v>
       </c>
       <c r="G45">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H45">
         <v>2.34</v>
@@ -11796,7 +11796,7 @@
         <v>0</v>
       </c>
       <c r="P45">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q45">
         <v>1.75</v>
@@ -12265,7 +12265,7 @@
         <v>5.7</v>
       </c>
       <c r="K47">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -12280,10 +12280,10 @@
         <v>0</v>
       </c>
       <c r="P47">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q47">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R47">
         <v>0</v>
@@ -12985,7 +12985,7 @@
         <v>4.4</v>
       </c>
       <c r="I50">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J50">
         <v>3.65</v>
@@ -13006,10 +13006,10 @@
         <v>0</v>
       </c>
       <c r="P50">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q50">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R50">
         <v>0</v>
@@ -13018,10 +13018,10 @@
         <v>0</v>
       </c>
       <c r="T50">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="U50">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="V50">
         <v>0</v>
@@ -13036,22 +13036,22 @@
         <v>16.5</v>
       </c>
       <c r="Z50">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA50">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB50">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AC50">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD50">
         <v>22</v>
       </c>
       <c r="AE50">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF50">
         <v>13.5</v>
@@ -13075,64 +13075,64 @@
         <v>48</v>
       </c>
       <c r="AM50">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN50">
         <v>17</v>
       </c>
       <c r="AO50">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AP50">
-        <v>11.5</v>
+        <v>4</v>
       </c>
       <c r="AQ50">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="AR50">
-        <v>4.7</v>
+        <v>22</v>
       </c>
       <c r="AS50">
         <v>5.1</v>
       </c>
       <c r="AT50">
-        <v>6.2</v>
+        <v>3.45</v>
       </c>
       <c r="AU50">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="AV50">
-        <v>16</v>
+        <v>4.3</v>
       </c>
       <c r="AW50">
         <v>5</v>
       </c>
       <c r="AX50">
-        <v>10</v>
+        <v>3.8</v>
       </c>
       <c r="AY50">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AZ50">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA50">
         <v>5</v>
       </c>
       <c r="BB50">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="BC50">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="BD50">
-        <v>34</v>
+        <v>4.8</v>
       </c>
       <c r="BE50">
         <v>5.1</v>
       </c>
       <c r="BF50">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BG50">
         <v>5</v>
@@ -13218,16 +13218,16 @@
         <v>240</v>
       </c>
       <c r="F51">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="G51">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="H51">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I51">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J51">
         <v>3.7</v>
@@ -13251,7 +13251,7 @@
         <v>1.87</v>
       </c>
       <c r="Q51">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R51">
         <v>0</v>
@@ -13260,7 +13260,7 @@
         <v>0</v>
       </c>
       <c r="T51">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U51">
         <v>1.97</v>
@@ -13323,7 +13323,7 @@
         <v>16.5</v>
       </c>
       <c r="AO51">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AP51">
         <v>10.5</v>
@@ -13335,7 +13335,7 @@
         <v>26</v>
       </c>
       <c r="AS51">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AT51">
         <v>7.2</v>
@@ -13347,7 +13347,7 @@
         <v>16</v>
       </c>
       <c r="AW51">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AX51">
         <v>8.4</v>
@@ -13356,16 +13356,16 @@
         <v>7.6</v>
       </c>
       <c r="AZ51">
-        <v>4.9</v>
+        <v>17.5</v>
       </c>
       <c r="BA51">
         <v>5.6</v>
       </c>
       <c r="BB51">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC51">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BD51">
         <v>5.3</v>
@@ -13460,10 +13460,10 @@
         <v>241</v>
       </c>
       <c r="F52">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="G52">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="H52">
         <v>3.2</v>
@@ -13493,7 +13493,7 @@
         <v>1.41</v>
       </c>
       <c r="Q52">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R52">
         <v>0</v>
@@ -13705,13 +13705,13 @@
         <v>3.1</v>
       </c>
       <c r="G53">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="H53">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="I53">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="J53">
         <v>2.98</v>
@@ -13732,10 +13732,10 @@
         <v>0</v>
       </c>
       <c r="P53">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Q53">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R53">
         <v>0</v>
@@ -13944,16 +13944,16 @@
         <v>243</v>
       </c>
       <c r="F54">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G54">
         <v>1.6</v>
       </c>
       <c r="H54">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I54">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J54">
         <v>3.9</v>
@@ -14186,22 +14186,22 @@
         <v>244</v>
       </c>
       <c r="F55">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G55">
         <v>3.75</v>
       </c>
       <c r="H55">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I55">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="J55">
         <v>3.15</v>
       </c>
       <c r="K55">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -14216,10 +14216,10 @@
         <v>0</v>
       </c>
       <c r="P55">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q55">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R55">
         <v>0</v>
@@ -14431,7 +14431,7 @@
         <v>2.5</v>
       </c>
       <c r="G56">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H56">
         <v>2.92</v>
@@ -14443,7 +14443,7 @@
         <v>3.05</v>
       </c>
       <c r="K56">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L56">
         <v>1.01</v>
@@ -14476,10 +14476,10 @@
         <v>1.11</v>
       </c>
       <c r="V56">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W56">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="X56">
         <v>1000</v>
@@ -14912,10 +14912,10 @@
         <v>247</v>
       </c>
       <c r="F58">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G58">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H58">
         <v>2</v>
@@ -14927,7 +14927,7 @@
         <v>3.5</v>
       </c>
       <c r="K58">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -14942,10 +14942,10 @@
         <v>0</v>
       </c>
       <c r="P58">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q58">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R58">
         <v>0</v>
@@ -15163,10 +15163,10 @@
         <v>4.6</v>
       </c>
       <c r="I59">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J59">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K59">
         <v>3.7</v>
@@ -15396,7 +15396,7 @@
         <v>249</v>
       </c>
       <c r="F60">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G60">
         <v>2.32</v>
@@ -15408,40 +15408,40 @@
         <v>4.5</v>
       </c>
       <c r="J60">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K60">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L60">
         <v>0</v>
       </c>
       <c r="M60">
+        <v>1.09</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>1.51</v>
+      </c>
+      <c r="Q60">
+        <v>2.36</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="T60">
         <v>1.11</v>
       </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
-      <c r="O60">
-        <v>0</v>
-      </c>
-      <c r="P60">
-        <v>1.58</v>
-      </c>
-      <c r="Q60">
-        <v>2.48</v>
-      </c>
-      <c r="R60">
-        <v>0</v>
-      </c>
-      <c r="S60">
-        <v>0</v>
-      </c>
-      <c r="T60">
-        <v>2.04</v>
-      </c>
       <c r="U60">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="V60">
         <v>0</v>
@@ -15450,112 +15450,112 @@
         <v>0</v>
       </c>
       <c r="X60">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Y60">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z60">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA60">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB60">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC60">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD60">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE60">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF60">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG60">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH60">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI60">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ60">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK60">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL60">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM60">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN60">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO60">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP60">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ60">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR60">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AS60">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT60">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AU60">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AV60">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW60">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX60">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY60">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ60">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BA60">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB60">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BC60">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BD60">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE60">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF60">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG60">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH60">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-01.xlsx
@@ -766,7 +766,7 @@
     <t>Sport Boys (Per)</t>
   </si>
   <si>
-    <t>2026-07-30 02:52:20</t>
+    <t>2026-07-30 05:02:17</t>
   </si>
 </sst>
 </file>
@@ -1360,7 +1360,7 @@
         <v>191</v>
       </c>
       <c r="F2">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="G2">
         <v>2.76</v>
@@ -1369,7 +1369,7 @@
         <v>2.78</v>
       </c>
       <c r="I2">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="J2">
         <v>3.4</v>
@@ -1378,16 +1378,16 @@
         <v>3.65</v>
       </c>
       <c r="L2">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M2">
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P2">
         <v>1.91</v>
@@ -1396,10 +1396,10 @@
         <v>1.97</v>
       </c>
       <c r="R2">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S2">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="T2">
         <v>1.77</v>
@@ -1408,16 +1408,16 @@
         <v>2.14</v>
       </c>
       <c r="V2">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
         <v>1.56</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y2">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="Z2">
         <v>28</v>
@@ -1426,10 +1426,10 @@
         <v>65</v>
       </c>
       <c r="AB2">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AC2">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2">
         <v>18.5</v>
@@ -1441,7 +1441,7 @@
         <v>25</v>
       </c>
       <c r="AG2">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
         <v>24</v>
@@ -1459,127 +1459,127 @@
         <v>55</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP2">
-        <v>2.28</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2">
-        <v>2</v>
+        <v>10.5</v>
       </c>
       <c r="AR2">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AS2">
-        <v>2.2</v>
+        <v>28</v>
       </c>
       <c r="AT2">
-        <v>1.99</v>
+        <v>9.6</v>
       </c>
       <c r="AU2">
-        <v>1.89</v>
+        <v>7.2</v>
       </c>
       <c r="AV2">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AW2">
-        <v>2.18</v>
+        <v>22</v>
       </c>
       <c r="AX2">
-        <v>2.08</v>
+        <v>15.5</v>
       </c>
       <c r="AY2">
-        <v>2</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>2.08</v>
+        <v>15</v>
       </c>
       <c r="BA2">
-        <v>2.2</v>
+        <v>29</v>
       </c>
       <c r="BB2">
-        <v>2.18</v>
+        <v>28</v>
       </c>
       <c r="BC2">
         <v>20</v>
       </c>
       <c r="BD2">
-        <v>2.18</v>
+        <v>28</v>
       </c>
       <c r="BE2">
-        <v>2.28</v>
+        <v>10</v>
       </c>
       <c r="BF2">
-        <v>2.28</v>
+        <v>18</v>
       </c>
       <c r="BG2">
-        <v>2.28</v>
+        <v>20</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI2">
-        <v>1.89</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="BK2">
-        <v>1.65</v>
+        <v>6.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.89</v>
+        <v>14</v>
       </c>
       <c r="BN2">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="BO2">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="BP2">
         <v>29</v>
       </c>
       <c r="BQ2">
-        <v>1.77</v>
+        <v>9</v>
       </c>
       <c r="BR2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BS2">
-        <v>1.82</v>
+        <v>10.5</v>
       </c>
       <c r="BT2">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="BU2">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="BV2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BW2">
-        <v>1.77</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2">
         <v>48</v>
       </c>
       <c r="BY2">
-        <v>1.82</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
         <v>38</v>
       </c>
       <c r="CA2">
-        <v>1.8</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="s">
         <v>250</v>
@@ -1620,13 +1620,13 @@
         <v>3.5</v>
       </c>
       <c r="L3">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="M3">
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="O3">
         <v>1.33</v>
@@ -1641,7 +1641,7 @@
         <v>1.24</v>
       </c>
       <c r="S3">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="T3">
         <v>1.6</v>
@@ -1853,10 +1853,10 @@
         <v>7.6</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J4">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K4">
         <v>4.6</v>
@@ -1865,31 +1865,31 @@
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="P4">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q4">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="R4">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="S4">
-        <v>2.48</v>
+        <v>4</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V4">
         <v>1.11</v>
@@ -1898,115 +1898,115 @@
         <v>2.6</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z4">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AB4">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD4">
         <v>42</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH4">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AP4">
-        <v>1.22</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
-        <v>1.22</v>
+        <v>15</v>
       </c>
       <c r="AR4">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="AS4">
-        <v>1.22</v>
+        <v>4.9</v>
       </c>
       <c r="AT4">
-        <v>1.06</v>
+        <v>5.7</v>
       </c>
       <c r="AU4">
-        <v>1.22</v>
+        <v>8</v>
       </c>
       <c r="AV4">
-        <v>1.19</v>
+        <v>4.3</v>
       </c>
       <c r="AW4">
-        <v>1.22</v>
+        <v>4.9</v>
       </c>
       <c r="AX4">
-        <v>1.22</v>
+        <v>6.8</v>
       </c>
       <c r="AY4">
-        <v>1.22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>1.18</v>
+        <v>21</v>
       </c>
       <c r="BA4">
-        <v>1.22</v>
+        <v>4.9</v>
       </c>
       <c r="BB4">
-        <v>1.22</v>
+        <v>10.5</v>
       </c>
       <c r="BC4">
-        <v>1.22</v>
+        <v>16.5</v>
       </c>
       <c r="BD4">
-        <v>1.22</v>
+        <v>4.6</v>
       </c>
       <c r="BE4">
-        <v>1.22</v>
+        <v>4.9</v>
       </c>
       <c r="BF4">
-        <v>1.22</v>
+        <v>8.4</v>
       </c>
       <c r="BG4">
-        <v>1.22</v>
+        <v>4.9</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI4">
         <v>1.01</v>
@@ -2015,55 +2015,55 @@
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BN4">
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BT4">
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="CB4" t="s">
         <v>250</v>
@@ -2086,22 +2086,22 @@
         <v>194</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G5">
         <v>5.7</v>
       </c>
       <c r="H5">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="I5">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L5">
         <v>1.33</v>
@@ -2110,13 +2110,13 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O5">
         <v>1.25</v>
       </c>
       <c r="P5">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q5">
         <v>1.71</v>
@@ -2131,7 +2131,7 @@
         <v>1.73</v>
       </c>
       <c r="U5">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V5">
         <v>2.28</v>
@@ -2287,7 +2287,7 @@
         <v>4.6</v>
       </c>
       <c r="BU5">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BV5">
         <v>11.5</v>
@@ -2331,28 +2331,28 @@
         <v>2.04</v>
       </c>
       <c r="G6">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H6">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I6">
         <v>4.2</v>
       </c>
       <c r="J6">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K6">
         <v>3.95</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M6">
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O6">
         <v>1.3</v>
@@ -2361,13 +2361,13 @@
         <v>1.89</v>
       </c>
       <c r="Q6">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="R6">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T6">
         <v>1.74</v>
@@ -2379,19 +2379,19 @@
         <v>1.32</v>
       </c>
       <c r="W6">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="X6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y6">
         <v>15.5</v>
       </c>
       <c r="Z6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA6">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB6">
         <v>11</v>
@@ -2430,7 +2430,7 @@
         <v>110</v>
       </c>
       <c r="AN6">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO6">
         <v>55</v>
@@ -2448,10 +2448,10 @@
         <v>1.03</v>
       </c>
       <c r="AT6">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU6">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV6">
         <v>1.03</v>
@@ -2466,7 +2466,7 @@
         <v>1.03</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA6">
         <v>1.03</v>
@@ -2475,7 +2475,7 @@
         <v>20</v>
       </c>
       <c r="BC6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD6">
         <v>1.03</v>
@@ -2490,16 +2490,16 @@
         <v>34</v>
       </c>
       <c r="BH6">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="BI6">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2508,46 +2508,46 @@
         <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="CB6" t="s">
         <v>250</v>
@@ -2570,112 +2570,112 @@
         <v>196</v>
       </c>
       <c r="F7">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="G7">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H7">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="I7">
+        <v>2.48</v>
+      </c>
+      <c r="J7">
+        <v>3.75</v>
+      </c>
+      <c r="K7">
+        <v>4.3</v>
+      </c>
+      <c r="L7">
+        <v>1.23</v>
+      </c>
+      <c r="M7">
+        <v>1.02</v>
+      </c>
+      <c r="N7">
+        <v>4.5</v>
+      </c>
+      <c r="O7">
+        <v>1.18</v>
+      </c>
+      <c r="P7">
         <v>2.54</v>
       </c>
-      <c r="J7">
-        <v>3.2</v>
-      </c>
-      <c r="K7">
-        <v>4</v>
-      </c>
-      <c r="L7">
-        <v>1.27</v>
-      </c>
-      <c r="M7">
-        <v>1.05</v>
-      </c>
-      <c r="N7">
-        <v>4.2</v>
-      </c>
-      <c r="O7">
-        <v>1.23</v>
-      </c>
-      <c r="P7">
-        <v>2.18</v>
-      </c>
       <c r="Q7">
+        <v>1.54</v>
+      </c>
+      <c r="R7">
+        <v>1.6</v>
+      </c>
+      <c r="S7">
+        <v>2.12</v>
+      </c>
+      <c r="T7">
+        <v>1.51</v>
+      </c>
+      <c r="U7">
+        <v>2.64</v>
+      </c>
+      <c r="V7">
         <v>1.67</v>
       </c>
-      <c r="R7">
-        <v>1.5</v>
-      </c>
-      <c r="S7">
-        <v>2.66</v>
-      </c>
-      <c r="T7">
-        <v>1.59</v>
-      </c>
-      <c r="U7">
-        <v>2.42</v>
-      </c>
-      <c r="V7">
-        <v>1.64</v>
-      </c>
       <c r="W7">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X7">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Y7">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="Z7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB7">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD7">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AE7">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AF7">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AG7">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH7">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AI7">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AJ7">
         <v>60</v>
       </c>
       <c r="AK7">
+        <v>36</v>
+      </c>
+      <c r="AL7">
         <v>40</v>
       </c>
-      <c r="AL7">
-        <v>46</v>
-      </c>
       <c r="AM7">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN7">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP7">
         <v>1.03</v>
@@ -2726,22 +2726,22 @@
         <v>1.03</v>
       </c>
       <c r="BF7">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="BG7">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BH7">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BI7">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BJ7">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BK7">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2750,46 +2750,46 @@
         <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP7">
+        <v>21</v>
+      </c>
+      <c r="BQ7">
+        <v>15</v>
+      </c>
+      <c r="BR7">
+        <v>27</v>
+      </c>
+      <c r="BS7">
+        <v>19</v>
+      </c>
+      <c r="BT7">
+        <v>5.8</v>
+      </c>
+      <c r="BU7">
+        <v>4.3</v>
+      </c>
+      <c r="BV7">
+        <v>15.5</v>
+      </c>
+      <c r="BW7">
+        <v>11</v>
+      </c>
+      <c r="BX7">
         <v>23</v>
       </c>
-      <c r="BQ7">
-        <v>15.5</v>
-      </c>
-      <c r="BR7">
-        <v>30</v>
-      </c>
-      <c r="BS7">
-        <v>21</v>
-      </c>
-      <c r="BT7">
-        <v>5.7</v>
-      </c>
-      <c r="BU7">
-        <v>4.2</v>
-      </c>
-      <c r="BV7">
+      <c r="BY7">
         <v>16.5</v>
       </c>
-      <c r="BW7">
-        <v>11.5</v>
-      </c>
-      <c r="BX7">
-        <v>26</v>
-      </c>
-      <c r="BY7">
-        <v>18</v>
-      </c>
       <c r="BZ7">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="CA7">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="CB7" t="s">
         <v>250</v>
@@ -2815,22 +2815,22 @@
         <v>2.44</v>
       </c>
       <c r="G8">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H8">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="I8">
         <v>3.1</v>
       </c>
       <c r="J8">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K8">
         <v>3.9</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M8">
         <v>1.05</v>
@@ -2845,10 +2845,10 @@
         <v>2.18</v>
       </c>
       <c r="Q8">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R8">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S8">
         <v>2.84</v>
@@ -2863,7 +2863,7 @@
         <v>1.48</v>
       </c>
       <c r="W8">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X8">
         <v>22</v>
@@ -2974,16 +2974,16 @@
         <v>16</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK8">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2992,46 +2992,46 @@
         <v>21</v>
       </c>
       <c r="BN8">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="BO8">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="BP8">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BR8">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BT8">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="BU8">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BV8">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BX8">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BZ8">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="CA8">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="CB8" t="s">
         <v>250</v>
@@ -3054,7 +3054,7 @@
         <v>198</v>
       </c>
       <c r="F9">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G9">
         <v>2.82</v>
@@ -3063,7 +3063,7 @@
         <v>2.76</v>
       </c>
       <c r="I9">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="J9">
         <v>3.4</v>
@@ -3084,7 +3084,7 @@
         <v>1.28</v>
       </c>
       <c r="P9">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q9">
         <v>1.86</v>
@@ -3096,13 +3096,13 @@
         <v>3.15</v>
       </c>
       <c r="T9">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U9">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V9">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W9">
         <v>1.55</v>
@@ -3222,58 +3222,58 @@
         <v>2.84</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK9">
-        <v>1.3</v>
+        <v>2.54</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.3</v>
+        <v>3.15</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO9">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ9">
-        <v>1.3</v>
+        <v>2.84</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS9">
-        <v>1.3</v>
+        <v>2.96</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU9">
-        <v>1.3</v>
+        <v>3.85</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW9">
-        <v>1.3</v>
+        <v>2.86</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY9">
-        <v>1.3</v>
+        <v>2.96</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA9">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="CB9" t="s">
         <v>250</v>
@@ -3538,22 +3538,22 @@
         <v>200</v>
       </c>
       <c r="F11">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G11">
         <v>3.2</v>
       </c>
       <c r="H11">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I11">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="J11">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K11">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3571,7 +3571,7 @@
         <v>2.26</v>
       </c>
       <c r="Q11">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>2.68</v>
       </c>
       <c r="G12">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="H12">
         <v>2.38</v>
@@ -3792,7 +3792,7 @@
         <v>2.7</v>
       </c>
       <c r="J12">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K12">
         <v>4.3</v>
@@ -4279,7 +4279,7 @@
         <v>5</v>
       </c>
       <c r="K14">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4506,22 +4506,22 @@
         <v>204</v>
       </c>
       <c r="F15">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="G15">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="H15">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J15">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K15">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4748,28 +4748,28 @@
         <v>205</v>
       </c>
       <c r="F16">
-        <v>1.02</v>
+        <v>2.94</v>
       </c>
       <c r="G16">
-        <v>990</v>
+        <v>3.4</v>
       </c>
       <c r="H16">
-        <v>1.02</v>
+        <v>2.48</v>
       </c>
       <c r="I16">
-        <v>990</v>
+        <v>2.86</v>
       </c>
       <c r="J16">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="K16">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4778,10 +4778,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="Q16">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4790,10 +4790,10 @@
         <v>0</v>
       </c>
       <c r="T16">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="U16">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -4802,112 +4802,112 @@
         <v>0</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH16">
         <v>0</v>
@@ -4990,28 +4990,28 @@
         <v>206</v>
       </c>
       <c r="F17">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="G17">
-        <v>990</v>
+        <v>4.1</v>
       </c>
       <c r="H17">
-        <v>1.02</v>
+        <v>1.99</v>
       </c>
       <c r="I17">
-        <v>990</v>
+        <v>2.18</v>
       </c>
       <c r="J17">
-        <v>1.02</v>
+        <v>3.4</v>
       </c>
       <c r="K17">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5020,10 +5020,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q17">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -5032,10 +5032,10 @@
         <v>0</v>
       </c>
       <c r="T17">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="U17">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -5044,112 +5044,112 @@
         <v>0</v>
       </c>
       <c r="X17">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC17">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD17">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE17">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG17">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH17">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI17">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK17">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP17">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AR17">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS17">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH17">
         <v>0</v>
@@ -5235,16 +5235,16 @@
         <v>1.38</v>
       </c>
       <c r="G18">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="H18">
         <v>8.4</v>
       </c>
       <c r="I18">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J18">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="K18">
         <v>6.4</v>
@@ -5262,10 +5262,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="Q18">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5964,7 +5964,7 @@
         <v>2.72</v>
       </c>
       <c r="H21">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I21">
         <v>3.2</v>
@@ -5973,7 +5973,7 @@
         <v>3.35</v>
       </c>
       <c r="K21">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5988,10 +5988,10 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="Q21">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -6215,7 +6215,7 @@
         <v>3.8</v>
       </c>
       <c r="K22">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6454,7 +6454,7 @@
         <v>5.2</v>
       </c>
       <c r="J23">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K23">
         <v>4.4</v>
@@ -6684,22 +6684,22 @@
         <v>213</v>
       </c>
       <c r="F24">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="G24">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="H24">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="I24">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="J24">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K24">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6714,10 +6714,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>2.14</v>
+        <v>2.42</v>
       </c>
       <c r="Q24">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>3.25</v>
       </c>
       <c r="G25">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H25">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I25">
         <v>2.4</v>
@@ -6941,7 +6941,7 @@
         <v>3.25</v>
       </c>
       <c r="K25">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -7168,19 +7168,19 @@
         <v>215</v>
       </c>
       <c r="F26">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="G26">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="H26">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="I26">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J26">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K26">
         <v>3.75</v>
@@ -7198,10 +7198,10 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="Q26">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -7906,7 +7906,7 @@
         <v>2.98</v>
       </c>
       <c r="J29">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K29">
         <v>4.2</v>
@@ -7924,7 +7924,7 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q29">
         <v>1.54</v>
@@ -8169,7 +8169,7 @@
         <v>1.57</v>
       </c>
       <c r="Q30">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -8381,7 +8381,7 @@
         <v>1.61</v>
       </c>
       <c r="G31">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H31">
         <v>4.9</v>
@@ -8408,10 +8408,10 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="Q31">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -8620,7 +8620,7 @@
         <v>221</v>
       </c>
       <c r="F32">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="G32">
         <v>6.2</v>
@@ -8653,7 +8653,7 @@
         <v>2.1</v>
       </c>
       <c r="Q32">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -8862,7 +8862,7 @@
         <v>222</v>
       </c>
       <c r="F33">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G33">
         <v>1.65</v>
@@ -8871,7 +8871,7 @@
         <v>6.2</v>
       </c>
       <c r="I33">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J33">
         <v>4.2</v>
@@ -8892,10 +8892,10 @@
         <v>0</v>
       </c>
       <c r="P33">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q33">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -9134,10 +9134,10 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q34">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -9346,13 +9346,13 @@
         <v>224</v>
       </c>
       <c r="F35">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G35">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H35">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I35">
         <v>6.2</v>
@@ -9361,7 +9361,7 @@
         <v>3.75</v>
       </c>
       <c r="K35">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -9379,7 +9379,7 @@
         <v>1.91</v>
       </c>
       <c r="Q35">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -9830,22 +9830,22 @@
         <v>226</v>
       </c>
       <c r="F37">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="G37">
         <v>1.28</v>
       </c>
       <c r="H37">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="I37">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J37">
         <v>6.2</v>
       </c>
       <c r="K37">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -9863,7 +9863,7 @@
         <v>2.12</v>
       </c>
       <c r="Q37">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -9872,10 +9872,10 @@
         <v>0</v>
       </c>
       <c r="T37">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U37">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V37">
         <v>0</v>
@@ -9890,7 +9890,7 @@
         <v>950</v>
       </c>
       <c r="Z37">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AA37">
         <v>1000</v>
@@ -9905,7 +9905,7 @@
         <v>950</v>
       </c>
       <c r="AE37">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AF37">
         <v>7.4</v>
@@ -9917,7 +9917,7 @@
         <v>55</v>
       </c>
       <c r="AI37">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="AJ37">
         <v>10.5</v>
@@ -9938,7 +9938,7 @@
         <v>1000</v>
       </c>
       <c r="AP37">
-        <v>4.8</v>
+        <v>17.5</v>
       </c>
       <c r="AQ37">
         <v>5.4</v>
@@ -9950,22 +9950,22 @@
         <v>6</v>
       </c>
       <c r="AT37">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU37">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="AV37">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW37">
         <v>6</v>
       </c>
       <c r="AX37">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AY37">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ37">
         <v>5.5</v>
@@ -9977,7 +9977,7 @@
         <v>7.4</v>
       </c>
       <c r="BC37">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="BD37">
         <v>5.5</v>
@@ -10072,22 +10072,22 @@
         <v>227</v>
       </c>
       <c r="F38">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="G38">
-        <v>600</v>
+        <v>3.85</v>
       </c>
       <c r="H38">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="I38">
-        <v>870</v>
+        <v>2.46</v>
       </c>
       <c r="J38">
-        <v>1.02</v>
+        <v>3.2</v>
       </c>
       <c r="K38">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -10102,10 +10102,10 @@
         <v>0</v>
       </c>
       <c r="P38">
-        <v>1.24</v>
+        <v>1.82</v>
       </c>
       <c r="Q38">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -10314,22 +10314,22 @@
         <v>228</v>
       </c>
       <c r="F39">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="G39">
-        <v>600</v>
+        <v>2.66</v>
       </c>
       <c r="H39">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="I39">
-        <v>870</v>
+        <v>3.4</v>
       </c>
       <c r="J39">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="K39">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -10344,10 +10344,10 @@
         <v>0</v>
       </c>
       <c r="P39">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="Q39">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -10556,7 +10556,7 @@
         <v>229</v>
       </c>
       <c r="F40">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G40">
         <v>7</v>
@@ -10571,7 +10571,7 @@
         <v>4.8</v>
       </c>
       <c r="K40">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -10798,22 +10798,22 @@
         <v>230</v>
       </c>
       <c r="F41">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="G41">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="H41">
-        <v>1.86</v>
+        <v>3.4</v>
       </c>
       <c r="I41">
+        <v>4.5</v>
+      </c>
+      <c r="J41">
         <v>4.2</v>
       </c>
-      <c r="J41">
-        <v>4.1</v>
-      </c>
       <c r="K41">
-        <v>950</v>
+        <v>5.1</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -10828,7 +10828,7 @@
         <v>0</v>
       </c>
       <c r="P41">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="Q41">
         <v>1.45</v>
@@ -11043,7 +11043,7 @@
         <v>2.16</v>
       </c>
       <c r="G42">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H42">
         <v>3.25</v>
@@ -11055,7 +11055,7 @@
         <v>3.45</v>
       </c>
       <c r="K42">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -11070,10 +11070,10 @@
         <v>0</v>
       </c>
       <c r="P42">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q42">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R42">
         <v>0</v>
@@ -11285,7 +11285,7 @@
         <v>1.68</v>
       </c>
       <c r="G43">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H43">
         <v>3.65</v>
@@ -11527,16 +11527,16 @@
         <v>2.46</v>
       </c>
       <c r="G44">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="H44">
         <v>2.88</v>
       </c>
       <c r="I44">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J44">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K44">
         <v>3.8</v>
@@ -11557,7 +11557,7 @@
         <v>1.88</v>
       </c>
       <c r="Q44">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -11766,23 +11766,23 @@
         <v>234</v>
       </c>
       <c r="F45">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G45">
         <v>3.25</v>
       </c>
       <c r="H45">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="I45">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="J45">
+        <v>3.65</v>
+      </c>
+      <c r="K45">
         <v>3.7</v>
       </c>
-      <c r="K45">
-        <v>3.8</v>
-      </c>
       <c r="L45">
         <v>0</v>
       </c>
@@ -11796,10 +11796,10 @@
         <v>0</v>
       </c>
       <c r="P45">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q45">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R45">
         <v>0</v>
@@ -12008,22 +12008,22 @@
         <v>235</v>
       </c>
       <c r="F46">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="G46">
+        <v>3.2</v>
+      </c>
+      <c r="H46">
+        <v>2.56</v>
+      </c>
+      <c r="I46">
+        <v>3.2</v>
+      </c>
+      <c r="J46">
         <v>3.3</v>
       </c>
-      <c r="H46">
-        <v>2.38</v>
-      </c>
-      <c r="I46">
-        <v>3.35</v>
-      </c>
-      <c r="J46">
-        <v>3.2</v>
-      </c>
       <c r="K46">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -12038,10 +12038,10 @@
         <v>0</v>
       </c>
       <c r="P46">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q46">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="R46">
         <v>0</v>
@@ -12253,16 +12253,16 @@
         <v>1.32</v>
       </c>
       <c r="G47">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="H47">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="I47">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="J47">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="K47">
         <v>6.8</v>
@@ -12976,10 +12976,10 @@
         <v>239</v>
       </c>
       <c r="F50">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G50">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H50">
         <v>4.4</v>
@@ -12991,13 +12991,13 @@
         <v>3.65</v>
       </c>
       <c r="K50">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L50">
         <v>0</v>
       </c>
       <c r="M50">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N50">
         <v>0</v>
@@ -13006,7 +13006,7 @@
         <v>0</v>
       </c>
       <c r="P50">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Q50">
         <v>2.02</v>
@@ -13018,10 +13018,10 @@
         <v>0</v>
       </c>
       <c r="T50">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="U50">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="V50">
         <v>0</v>
@@ -13042,10 +13042,10 @@
         <v>130</v>
       </c>
       <c r="AB50">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AC50">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD50">
         <v>22</v>
@@ -13060,7 +13060,7 @@
         <v>12.5</v>
       </c>
       <c r="AH50">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI50">
         <v>75</v>
@@ -13084,31 +13084,31 @@
         <v>85</v>
       </c>
       <c r="AP50">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AQ50">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AR50">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS50">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AT50">
-        <v>3.45</v>
+        <v>7.4</v>
       </c>
       <c r="AU50">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AV50">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AW50">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AX50">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AY50">
         <v>7.8</v>
@@ -13117,25 +13117,25 @@
         <v>14.5</v>
       </c>
       <c r="BA50">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB50">
-        <v>15.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC50">
         <v>15</v>
       </c>
       <c r="BD50">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BE50">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BF50">
         <v>10.5</v>
       </c>
       <c r="BG50">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BH50">
         <v>0</v>
@@ -13218,7 +13218,7 @@
         <v>240</v>
       </c>
       <c r="F51">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G51">
         <v>1.93</v>
@@ -13233,7 +13233,7 @@
         <v>3.7</v>
       </c>
       <c r="K51">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -13490,7 +13490,7 @@
         <v>0</v>
       </c>
       <c r="P52">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -13708,13 +13708,13 @@
         <v>3.5</v>
       </c>
       <c r="H53">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="I53">
         <v>2.88</v>
       </c>
       <c r="J53">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K53">
         <v>3.2</v>
@@ -13735,7 +13735,7 @@
         <v>1.55</v>
       </c>
       <c r="Q53">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="R53">
         <v>0</v>
@@ -13953,13 +13953,13 @@
         <v>8</v>
       </c>
       <c r="I54">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J54">
         <v>3.9</v>
       </c>
       <c r="K54">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -13974,10 +13974,10 @@
         <v>0</v>
       </c>
       <c r="P54">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="Q54">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="R54">
         <v>0</v>
@@ -14189,19 +14189,19 @@
         <v>3.1</v>
       </c>
       <c r="G55">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H55">
         <v>2.38</v>
       </c>
       <c r="I55">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J55">
         <v>3.15</v>
       </c>
       <c r="K55">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -14219,7 +14219,7 @@
         <v>1.65</v>
       </c>
       <c r="Q55">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R55">
         <v>0</v>
@@ -14428,22 +14428,22 @@
         <v>245</v>
       </c>
       <c r="F56">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G56">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="H56">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="I56">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J56">
         <v>3.05</v>
       </c>
       <c r="K56">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L56">
         <v>1.01</v>
@@ -14452,7 +14452,7 @@
         <v>1.01</v>
       </c>
       <c r="N56">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="O56">
         <v>1.4</v>
@@ -14464,55 +14464,55 @@
         <v>2.16</v>
       </c>
       <c r="R56">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S56">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="T56">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="U56">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V56">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W56">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X56">
         <v>1000</v>
       </c>
       <c r="Y56">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z56">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA56">
         <v>1000</v>
       </c>
       <c r="AB56">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC56">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD56">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE56">
         <v>1000</v>
       </c>
       <c r="AF56">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG56">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH56">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI56">
         <v>1000</v>
@@ -14521,7 +14521,7 @@
         <v>1000</v>
       </c>
       <c r="AK56">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL56">
         <v>1000</v>
@@ -14536,58 +14536,58 @@
         <v>1000</v>
       </c>
       <c r="AP56">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="AQ56">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR56">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AS56">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="AT56">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU56">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AV56">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW56">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="AX56">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY56">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ56">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BA56">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BB56">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BC56">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BD56">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BE56">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BF56">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BG56">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BH56">
         <v>1000</v>
@@ -14670,19 +14670,19 @@
         <v>246</v>
       </c>
       <c r="F57">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="G57">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="H57">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="I57">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="J57">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K57">
         <v>3.45</v>
@@ -14700,10 +14700,10 @@
         <v>0</v>
       </c>
       <c r="P57">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="Q57">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="R57">
         <v>0</v>
@@ -14912,7 +14912,7 @@
         <v>247</v>
       </c>
       <c r="F58">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G58">
         <v>4.3</v>
@@ -14924,7 +14924,7 @@
         <v>2.22</v>
       </c>
       <c r="J58">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K58">
         <v>4</v>
@@ -14945,7 +14945,7 @@
         <v>1.96</v>
       </c>
       <c r="Q58">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R58">
         <v>0</v>
@@ -15166,7 +15166,7 @@
         <v>5.5</v>
       </c>
       <c r="J59">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K59">
         <v>3.7</v>
@@ -15184,10 +15184,10 @@
         <v>0</v>
       </c>
       <c r="P59">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q59">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R59">
         <v>0</v>
@@ -15396,7 +15396,7 @@
         <v>249</v>
       </c>
       <c r="F60">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G60">
         <v>2.32</v>
@@ -15408,154 +15408,154 @@
         <v>4.5</v>
       </c>
       <c r="J60">
+        <v>3</v>
+      </c>
+      <c r="K60">
+        <v>3.35</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>1.11</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>1.58</v>
+      </c>
+      <c r="Q60">
+        <v>2.38</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="T60">
+        <v>2.04</v>
+      </c>
+      <c r="U60">
+        <v>1.81</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0</v>
+      </c>
+      <c r="X60">
+        <v>9.6</v>
+      </c>
+      <c r="Y60">
+        <v>14.5</v>
+      </c>
+      <c r="Z60">
+        <v>36</v>
+      </c>
+      <c r="AA60">
+        <v>120</v>
+      </c>
+      <c r="AB60">
+        <v>7.6</v>
+      </c>
+      <c r="AC60">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD60">
+        <v>22</v>
+      </c>
+      <c r="AE60">
+        <v>80</v>
+      </c>
+      <c r="AF60">
+        <v>15.5</v>
+      </c>
+      <c r="AG60">
+        <v>14</v>
+      </c>
+      <c r="AH60">
+        <v>27</v>
+      </c>
+      <c r="AI60">
+        <v>110</v>
+      </c>
+      <c r="AJ60">
+        <v>38</v>
+      </c>
+      <c r="AK60">
+        <v>36</v>
+      </c>
+      <c r="AL60">
+        <v>70</v>
+      </c>
+      <c r="AM60">
+        <v>200</v>
+      </c>
+      <c r="AN60">
+        <v>34</v>
+      </c>
+      <c r="AO60">
+        <v>120</v>
+      </c>
+      <c r="AP60">
+        <v>3.35</v>
+      </c>
+      <c r="AQ60">
+        <v>3.85</v>
+      </c>
+      <c r="AR60">
+        <v>4.5</v>
+      </c>
+      <c r="AS60">
+        <v>5</v>
+      </c>
+      <c r="AT60">
         <v>3.1</v>
       </c>
-      <c r="K60">
-        <v>3.45</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60">
-        <v>1.09</v>
-      </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
-      <c r="O60">
-        <v>0</v>
-      </c>
-      <c r="P60">
-        <v>1.51</v>
-      </c>
-      <c r="Q60">
-        <v>2.36</v>
-      </c>
-      <c r="R60">
-        <v>0</v>
-      </c>
-      <c r="S60">
-        <v>0</v>
-      </c>
-      <c r="T60">
-        <v>1.11</v>
-      </c>
-      <c r="U60">
-        <v>1.73</v>
-      </c>
-      <c r="V60">
-        <v>0</v>
-      </c>
-      <c r="W60">
-        <v>0</v>
-      </c>
-      <c r="X60">
-        <v>1000</v>
-      </c>
-      <c r="Y60">
-        <v>1000</v>
-      </c>
-      <c r="Z60">
-        <v>1000</v>
-      </c>
-      <c r="AA60">
-        <v>1000</v>
-      </c>
-      <c r="AB60">
-        <v>1000</v>
-      </c>
-      <c r="AC60">
-        <v>1000</v>
-      </c>
-      <c r="AD60">
-        <v>1000</v>
-      </c>
-      <c r="AE60">
-        <v>1000</v>
-      </c>
-      <c r="AF60">
-        <v>1000</v>
-      </c>
-      <c r="AG60">
-        <v>1000</v>
-      </c>
-      <c r="AH60">
-        <v>1000</v>
-      </c>
-      <c r="AI60">
-        <v>1000</v>
-      </c>
-      <c r="AJ60">
-        <v>1000</v>
-      </c>
-      <c r="AK60">
-        <v>1000</v>
-      </c>
-      <c r="AL60">
-        <v>1000</v>
-      </c>
-      <c r="AM60">
-        <v>1000</v>
-      </c>
-      <c r="AN60">
-        <v>1000</v>
-      </c>
-      <c r="AO60">
-        <v>1000</v>
-      </c>
-      <c r="AP60">
-        <v>1.01</v>
-      </c>
-      <c r="AQ60">
-        <v>1.01</v>
-      </c>
-      <c r="AR60">
-        <v>1.01</v>
-      </c>
-      <c r="AS60">
-        <v>1.01</v>
-      </c>
-      <c r="AT60">
-        <v>1.01</v>
-      </c>
       <c r="AU60">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV60">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW60">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX60">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY60">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ60">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA60">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB60">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC60">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD60">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE60">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF60">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG60">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH60">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-01.xlsx
@@ -766,7 +766,7 @@
     <t>Sport Boys (Per)</t>
   </si>
   <si>
-    <t>2026-07-30 05:02:17</t>
+    <t>2026-07-30 07:11:59</t>
   </si>
 </sst>
 </file>
@@ -1360,16 +1360,16 @@
         <v>191</v>
       </c>
       <c r="F2">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="G2">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H2">
         <v>2.78</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="J2">
         <v>3.4</v>
@@ -1378,46 +1378,46 @@
         <v>3.65</v>
       </c>
       <c r="L2">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M2">
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O2">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="Q2">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="R2">
         <v>1.34</v>
       </c>
       <c r="S2">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="T2">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U2">
         <v>2.14</v>
       </c>
       <c r="V2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W2">
         <v>1.56</v>
       </c>
       <c r="X2">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z2">
         <v>28</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="AC2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD2">
         <v>18.5</v>
@@ -1468,10 +1468,10 @@
         <v>40</v>
       </c>
       <c r="AP2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR2">
         <v>17</v>
@@ -1513,7 +1513,7 @@
         <v>28</v>
       </c>
       <c r="BE2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF2">
         <v>18</v>
@@ -1522,22 +1522,22 @@
         <v>20</v>
       </c>
       <c r="BH2">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BI2">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="BJ2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK2">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN2">
         <v>5.8</v>
@@ -1549,16 +1549,16 @@
         <v>29</v>
       </c>
       <c r="BQ2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BR2">
         <v>46</v>
       </c>
       <c r="BS2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU2">
         <v>5.2</v>
@@ -1567,19 +1567,19 @@
         <v>30</v>
       </c>
       <c r="BW2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
         <v>48</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ2">
         <v>38</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB2" t="s">
         <v>250</v>
@@ -1608,10 +1608,10 @@
         <v>3.2</v>
       </c>
       <c r="H3">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I3">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="J3">
         <v>3.15</v>
@@ -1620,7 +1620,7 @@
         <v>3.5</v>
       </c>
       <c r="L3">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="M3">
         <v>1.01</v>
@@ -1629,16 +1629,16 @@
         <v>3.35</v>
       </c>
       <c r="O3">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P3">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S3">
         <v>3</v>
@@ -1650,7 +1650,7 @@
         <v>1.84</v>
       </c>
       <c r="V3">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W3">
         <v>1.45</v>
@@ -1767,22 +1767,22 @@
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="BJ3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK3">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="BN3">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO3">
         <v>3.85</v>
@@ -1791,16 +1791,16 @@
         <v>34</v>
       </c>
       <c r="BQ3">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="BT3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU3">
         <v>3.7</v>
@@ -1809,19 +1809,19 @@
         <v>30</v>
       </c>
       <c r="BW3">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="BX3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY3">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="BZ3">
         <v>46</v>
       </c>
       <c r="CA3">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="CB3" t="s">
         <v>250</v>
@@ -1859,25 +1859,25 @@
         <v>3.9</v>
       </c>
       <c r="K4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
         <v>3.1</v>
       </c>
       <c r="O4">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P4">
         <v>1.72</v>
       </c>
       <c r="Q4">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R4">
         <v>1.27</v>
@@ -1886,7 +1886,7 @@
         <v>4</v>
       </c>
       <c r="T4">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U4">
         <v>1.68</v>
@@ -1898,10 +1898,10 @@
         <v>2.6</v>
       </c>
       <c r="X4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z4">
         <v>90</v>
@@ -1910,7 +1910,7 @@
         <v>420</v>
       </c>
       <c r="AB4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC4">
         <v>11.5</v>
@@ -1958,10 +1958,10 @@
         <v>15</v>
       </c>
       <c r="AR4">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AS4">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT4">
         <v>5.7</v>
@@ -1970,10 +1970,10 @@
         <v>8</v>
       </c>
       <c r="AV4">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AW4">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX4">
         <v>6.8</v>
@@ -1985,7 +1985,7 @@
         <v>21</v>
       </c>
       <c r="BA4">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB4">
         <v>10.5</v>
@@ -1994,22 +1994,22 @@
         <v>16.5</v>
       </c>
       <c r="BD4">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE4">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG4">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH4">
         <v>4.2</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
@@ -2086,16 +2086,16 @@
         <v>194</v>
       </c>
       <c r="F5">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="G5">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="H5">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="I5">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="J5">
         <v>4.1</v>
@@ -2104,7 +2104,7 @@
         <v>4.5</v>
       </c>
       <c r="L5">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M5">
         <v>1.05</v>
@@ -2119,31 +2119,31 @@
         <v>2.18</v>
       </c>
       <c r="Q5">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R5">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S5">
         <v>2.84</v>
       </c>
       <c r="T5">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="U5">
         <v>2.14</v>
       </c>
       <c r="V5">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="W5">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X5">
         <v>19.5</v>
       </c>
       <c r="Y5">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z5">
         <v>13</v>
@@ -2194,7 +2194,7 @@
         <v>9</v>
       </c>
       <c r="AP5">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AQ5">
         <v>8.800000000000001</v>
@@ -2206,7 +2206,7 @@
         <v>15.5</v>
       </c>
       <c r="AT5">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AU5">
         <v>8.6</v>
@@ -2218,37 +2218,37 @@
         <v>15</v>
       </c>
       <c r="AX5">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AY5">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AZ5">
         <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB5">
+        <v>6.2</v>
+      </c>
+      <c r="BC5">
         <v>6</v>
       </c>
-      <c r="BC5">
-        <v>5.8</v>
-      </c>
       <c r="BD5">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE5">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF5">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG5">
         <v>7</v>
       </c>
       <c r="BH5">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI5">
         <v>3.15</v>
@@ -2257,55 +2257,55 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
         <v>8.800000000000001</v>
       </c>
       <c r="BO5">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
         <v>65</v>
       </c>
       <c r="BS5">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BU5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BV5">
         <v>11.5</v>
       </c>
       <c r="BW5">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BX5">
         <v>24</v>
       </c>
       <c r="BY5">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="CA5">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
         <v>250</v>
@@ -2328,25 +2328,25 @@
         <v>195</v>
       </c>
       <c r="F6">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G6">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="H6">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I6">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K6">
         <v>3.95</v>
       </c>
       <c r="L6">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M6">
         <v>1.07</v>
@@ -2358,28 +2358,28 @@
         <v>1.3</v>
       </c>
       <c r="P6">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="Q6">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R6">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S6">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T6">
         <v>1.74</v>
       </c>
       <c r="U6">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W6">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="X6">
         <v>16.5</v>
@@ -2391,7 +2391,7 @@
         <v>32</v>
       </c>
       <c r="AA6">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB6">
         <v>11</v>
@@ -2406,7 +2406,7 @@
         <v>55</v>
       </c>
       <c r="AF6">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AG6">
         <v>12.5</v>
@@ -2415,7 +2415,7 @@
         <v>21</v>
       </c>
       <c r="AI6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ6">
         <v>29</v>
@@ -2436,7 +2436,7 @@
         <v>55</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ6">
         <v>1.03</v>
@@ -2463,7 +2463,7 @@
         <v>1.03</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ6">
         <v>13.5</v>
@@ -2493,19 +2493,19 @@
         <v>3.55</v>
       </c>
       <c r="BI6">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ6">
         <v>10</v>
       </c>
       <c r="BK6">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN6">
         <v>5.2</v>
@@ -2514,40 +2514,40 @@
         <v>4</v>
       </c>
       <c r="BP6">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ6">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS6">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="BT6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU6">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>22</v>
+        <v>7.8</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>30</v>
+        <v>8.4</v>
       </c>
       <c r="BZ6">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>19</v>
+        <v>7.4</v>
       </c>
       <c r="CB6" t="s">
         <v>250</v>
@@ -2735,61 +2735,61 @@
         <v>4.6</v>
       </c>
       <c r="BI7">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
         <v>8.6</v>
       </c>
       <c r="BK7">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
         <v>6.8</v>
       </c>
       <c r="BO7">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
         <v>21</v>
       </c>
       <c r="BQ7">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>27</v>
       </c>
       <c r="BS7">
-        <v>19</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
         <v>5.8</v>
       </c>
       <c r="BU7">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>15.5</v>
       </c>
       <c r="BW7">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>23</v>
       </c>
       <c r="BY7">
-        <v>16.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>16</v>
       </c>
       <c r="CA7">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
         <v>250</v>
@@ -2842,25 +2842,25 @@
         <v>1.25</v>
       </c>
       <c r="P8">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q8">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="R8">
         <v>1.48</v>
       </c>
       <c r="S8">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T8">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U8">
         <v>2.4</v>
       </c>
       <c r="V8">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W8">
         <v>1.62</v>
@@ -2974,64 +2974,64 @@
         <v>16</v>
       </c>
       <c r="BH8">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI8">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="BJ8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK8">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
         <v>5.7</v>
       </c>
       <c r="BO8">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>19.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU8">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW8">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>14.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
         <v>250</v>
@@ -3057,19 +3057,19 @@
         <v>2.62</v>
       </c>
       <c r="G9">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="H9">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="I9">
         <v>2.96</v>
       </c>
       <c r="J9">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K9">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -3099,13 +3099,13 @@
         <v>1.69</v>
       </c>
       <c r="U9">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V9">
         <v>1.51</v>
       </c>
       <c r="W9">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X9">
         <v>16.5</v>
@@ -3225,7 +3225,7 @@
         <v>13</v>
       </c>
       <c r="BK9">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BL9">
         <v>1000</v>
@@ -3237,28 +3237,28 @@
         <v>8</v>
       </c>
       <c r="BO9">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BP9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ9">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BR9">
         <v>46</v>
       </c>
       <c r="BS9">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BT9">
         <v>8.6</v>
       </c>
       <c r="BU9">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BV9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW9">
         <v>2.86</v>
@@ -3267,13 +3267,13 @@
         <v>48</v>
       </c>
       <c r="BY9">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BZ9">
         <v>36</v>
       </c>
       <c r="CA9">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CB9" t="s">
         <v>250</v>
@@ -3314,28 +3314,28 @@
         <v>950</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P10">
         <v>1.25</v>
       </c>
       <c r="Q10">
+        <v>1.02</v>
+      </c>
+      <c r="R10">
+        <v>1.07</v>
+      </c>
+      <c r="S10">
         <v>1.01</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3344,10 +3344,10 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3458,64 +3458,64 @@
         <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
         <v>250</v>
@@ -3538,22 +3538,22 @@
         <v>200</v>
       </c>
       <c r="F11">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G11">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="H11">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="I11">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="J11">
         <v>3.65</v>
       </c>
       <c r="K11">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3568,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q11">
         <v>1.55</v>
@@ -4267,16 +4267,16 @@
         <v>1.58</v>
       </c>
       <c r="G14">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="H14">
+        <v>4.8</v>
+      </c>
+      <c r="I14">
+        <v>6.2</v>
+      </c>
+      <c r="J14">
         <v>4.9</v>
-      </c>
-      <c r="I14">
-        <v>6</v>
-      </c>
-      <c r="J14">
-        <v>5</v>
       </c>
       <c r="K14">
         <v>5.5</v>
@@ -4506,7 +4506,7 @@
         <v>204</v>
       </c>
       <c r="F15">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G15">
         <v>1.94</v>
@@ -4539,7 +4539,7 @@
         <v>3.25</v>
       </c>
       <c r="Q15">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4790,10 +4790,10 @@
         <v>0</v>
       </c>
       <c r="T16">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U16">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -5071,7 +5071,7 @@
         <v>34</v>
       </c>
       <c r="AG17">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH17">
         <v>19.5</v>
@@ -5098,31 +5098,31 @@
         <v>15.5</v>
       </c>
       <c r="AP17">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ17">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AR17">
+        <v>4.1</v>
+      </c>
+      <c r="AS17">
+        <v>4.6</v>
+      </c>
+      <c r="AT17">
         <v>4.2</v>
       </c>
-      <c r="AS17">
-        <v>4.7</v>
-      </c>
-      <c r="AT17">
-        <v>4.3</v>
-      </c>
       <c r="AU17">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AV17">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AW17">
         <v>4.5</v>
       </c>
       <c r="AX17">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AY17">
         <v>4.2</v>
@@ -5131,25 +5131,25 @@
         <v>4.3</v>
       </c>
       <c r="BA17">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB17">
         <v>5.2</v>
       </c>
       <c r="BC17">
+        <v>4.9</v>
+      </c>
+      <c r="BD17">
         <v>5</v>
       </c>
-      <c r="BD17">
-        <v>5.1</v>
-      </c>
       <c r="BE17">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF17">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BG17">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BH17">
         <v>0</v>
@@ -5244,7 +5244,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="J18">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K18">
         <v>6.4</v>
@@ -5262,7 +5262,7 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="Q18">
         <v>1.44</v>
@@ -5964,13 +5964,13 @@
         <v>2.72</v>
       </c>
       <c r="H21">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="I21">
         <v>3.2</v>
       </c>
       <c r="J21">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K21">
         <v>3.85</v>
@@ -5991,7 +5991,7 @@
         <v>1.94</v>
       </c>
       <c r="Q21">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -6200,19 +6200,19 @@
         <v>211</v>
       </c>
       <c r="F22">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G22">
         <v>2.22</v>
       </c>
       <c r="H22">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I22">
         <v>4.1</v>
       </c>
       <c r="J22">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K22">
         <v>4.3</v>
@@ -6230,7 +6230,7 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q22">
         <v>1.64</v>
@@ -6442,7 +6442,7 @@
         <v>212</v>
       </c>
       <c r="F23">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G23">
         <v>1.89</v>
@@ -6457,7 +6457,7 @@
         <v>3.9</v>
       </c>
       <c r="K23">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6475,7 +6475,7 @@
         <v>2.18</v>
       </c>
       <c r="Q23">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6684,13 +6684,13 @@
         <v>213</v>
       </c>
       <c r="F24">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="G24">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="H24">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I24">
         <v>4.6</v>
@@ -6699,7 +6699,7 @@
         <v>4</v>
       </c>
       <c r="K24">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6714,10 +6714,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>2.42</v>
+        <v>1.25</v>
       </c>
       <c r="Q24">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6938,10 +6938,10 @@
         <v>2.4</v>
       </c>
       <c r="J25">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K25">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -7198,10 +7198,10 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q26">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -7655,10 +7655,10 @@
         <v>2.04</v>
       </c>
       <c r="G28">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H28">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="I28">
         <v>4</v>
@@ -7906,7 +7906,7 @@
         <v>2.98</v>
       </c>
       <c r="J29">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K29">
         <v>4.2</v>
@@ -8139,10 +8139,10 @@
         <v>2.14</v>
       </c>
       <c r="G30">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H30">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I30">
         <v>4.5</v>
@@ -8169,7 +8169,7 @@
         <v>1.57</v>
       </c>
       <c r="Q30">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -8202,7 +8202,7 @@
         <v>110</v>
       </c>
       <c r="AB30">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC30">
         <v>8.199999999999999</v>
@@ -8214,7 +8214,7 @@
         <v>70</v>
       </c>
       <c r="AF30">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG30">
         <v>13</v>
@@ -8253,7 +8253,7 @@
         <v>21</v>
       </c>
       <c r="AS30">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT30">
         <v>6.2</v>
@@ -8265,7 +8265,7 @@
         <v>13</v>
       </c>
       <c r="AW30">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX30">
         <v>10</v>
@@ -8277,25 +8277,25 @@
         <v>17</v>
       </c>
       <c r="BA30">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB30">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC30">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BD30">
+        <v>7.4</v>
+      </c>
+      <c r="BE30">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF30">
         <v>6.6</v>
       </c>
-      <c r="BE30">
-        <v>7.2</v>
-      </c>
-      <c r="BF30">
-        <v>6</v>
-      </c>
       <c r="BG30">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BH30">
         <v>0</v>
@@ -8381,10 +8381,10 @@
         <v>1.61</v>
       </c>
       <c r="G31">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H31">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I31">
         <v>6.2</v>
@@ -8408,7 +8408,7 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="Q31">
         <v>1.48</v>
@@ -8623,10 +8623,10 @@
         <v>4.9</v>
       </c>
       <c r="G32">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="H32">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="I32">
         <v>1.79</v>
@@ -8650,10 +8650,10 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q32">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -8865,13 +8865,13 @@
         <v>1.57</v>
       </c>
       <c r="G33">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="H33">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J33">
         <v>4.2</v>
@@ -8892,10 +8892,10 @@
         <v>0</v>
       </c>
       <c r="P33">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q33">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -9104,7 +9104,7 @@
         <v>223</v>
       </c>
       <c r="F34">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="G34">
         <v>4.6</v>
@@ -9134,10 +9134,10 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q34">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -9346,7 +9346,7 @@
         <v>224</v>
       </c>
       <c r="F35">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G35">
         <v>1.84</v>
@@ -9355,7 +9355,7 @@
         <v>5.1</v>
       </c>
       <c r="I35">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J35">
         <v>3.75</v>
@@ -9376,7 +9376,7 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q35">
         <v>1.9</v>
@@ -9588,10 +9588,10 @@
         <v>225</v>
       </c>
       <c r="F36">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="G36">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="H36">
         <v>2.64</v>
@@ -9600,7 +9600,7 @@
         <v>2.98</v>
       </c>
       <c r="J36">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K36">
         <v>3.4</v>
@@ -9836,7 +9836,7 @@
         <v>1.28</v>
       </c>
       <c r="H37">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="I37">
         <v>23</v>
@@ -9845,7 +9845,7 @@
         <v>6.2</v>
       </c>
       <c r="K37">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -9863,7 +9863,7 @@
         <v>2.12</v>
       </c>
       <c r="Q37">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -9872,10 +9872,10 @@
         <v>0</v>
       </c>
       <c r="T37">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="U37">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="V37">
         <v>0</v>
@@ -9905,7 +9905,7 @@
         <v>950</v>
       </c>
       <c r="AE37">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AF37">
         <v>7.4</v>
@@ -9917,7 +9917,7 @@
         <v>55</v>
       </c>
       <c r="AI37">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="AJ37">
         <v>10.5</v>
@@ -9929,7 +9929,7 @@
         <v>60</v>
       </c>
       <c r="AM37">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="AN37">
         <v>5.6</v>
@@ -9956,13 +9956,13 @@
         <v>12.5</v>
       </c>
       <c r="AV37">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AW37">
         <v>6</v>
       </c>
       <c r="AX37">
-        <v>3.35</v>
+        <v>5.8</v>
       </c>
       <c r="AY37">
         <v>9.800000000000001</v>
@@ -10072,22 +10072,22 @@
         <v>227</v>
       </c>
       <c r="F38">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="G38">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="H38">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="I38">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="J38">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K38">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -10102,10 +10102,10 @@
         <v>0</v>
       </c>
       <c r="P38">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="Q38">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -10317,19 +10317,19 @@
         <v>2.32</v>
       </c>
       <c r="G39">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H39">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I39">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J39">
         <v>3.35</v>
       </c>
       <c r="K39">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -10344,10 +10344,10 @@
         <v>0</v>
       </c>
       <c r="P39">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="Q39">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -10556,16 +10556,16 @@
         <v>229</v>
       </c>
       <c r="F40">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="G40">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H40">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I40">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="J40">
         <v>4.8</v>
@@ -10589,7 +10589,7 @@
         <v>2.62</v>
       </c>
       <c r="Q40">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -10798,7 +10798,7 @@
         <v>230</v>
       </c>
       <c r="F41">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="G41">
         <v>2.08</v>
@@ -10807,13 +10807,13 @@
         <v>3.4</v>
       </c>
       <c r="I41">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J41">
         <v>4.2</v>
       </c>
       <c r="K41">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -10831,7 +10831,7 @@
         <v>3</v>
       </c>
       <c r="Q41">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -11046,7 +11046,7 @@
         <v>2.38</v>
       </c>
       <c r="H42">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I42">
         <v>3.8</v>
@@ -11055,7 +11055,7 @@
         <v>3.45</v>
       </c>
       <c r="K42">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -11070,10 +11070,10 @@
         <v>0</v>
       </c>
       <c r="P42">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q42">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R42">
         <v>0</v>
@@ -11282,22 +11282,22 @@
         <v>232</v>
       </c>
       <c r="F43">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="G43">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="H43">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="I43">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="J43">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K43">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -11524,13 +11524,13 @@
         <v>233</v>
       </c>
       <c r="F44">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G44">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H44">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I44">
         <v>3.2</v>
@@ -11539,7 +11539,7 @@
         <v>3.35</v>
       </c>
       <c r="K44">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -11554,10 +11554,10 @@
         <v>0</v>
       </c>
       <c r="P44">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q44">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -11766,16 +11766,16 @@
         <v>234</v>
       </c>
       <c r="F45">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G45">
         <v>3.25</v>
       </c>
       <c r="H45">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I45">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="J45">
         <v>3.65</v>
@@ -11796,10 +11796,10 @@
         <v>0</v>
       </c>
       <c r="P45">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q45">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="R45">
         <v>0</v>
@@ -12008,19 +12008,19 @@
         <v>235</v>
       </c>
       <c r="F46">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G46">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="H46">
         <v>2.56</v>
       </c>
       <c r="I46">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="J46">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K46">
         <v>4.1</v>
@@ -12492,22 +12492,22 @@
         <v>237</v>
       </c>
       <c r="F48">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="G48">
-        <v>600</v>
+        <v>1.53</v>
       </c>
       <c r="H48">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="I48">
-        <v>870</v>
+        <v>8.4</v>
       </c>
       <c r="J48">
-        <v>1.18</v>
+        <v>4.3</v>
       </c>
       <c r="K48">
-        <v>950</v>
+        <v>5.7</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -12522,10 +12522,10 @@
         <v>0</v>
       </c>
       <c r="P48">
-        <v>1.24</v>
+        <v>2.52</v>
       </c>
       <c r="Q48">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="R48">
         <v>0</v>
@@ -13126,7 +13126,7 @@
         <v>15</v>
       </c>
       <c r="BD50">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BE50">
         <v>5.7</v>
@@ -13463,7 +13463,7 @@
         <v>2.7</v>
       </c>
       <c r="G52">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H52">
         <v>3.2</v>
@@ -13472,7 +13472,7 @@
         <v>3.5</v>
       </c>
       <c r="J52">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K52">
         <v>3</v>
@@ -13944,7 +13944,7 @@
         <v>243</v>
       </c>
       <c r="F54">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="G54">
         <v>1.6</v>
@@ -13956,10 +13956,10 @@
         <v>10</v>
       </c>
       <c r="J54">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K54">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -14192,16 +14192,16 @@
         <v>3.7</v>
       </c>
       <c r="H55">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I55">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J55">
         <v>3.15</v>
       </c>
       <c r="K55">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -14216,10 +14216,10 @@
         <v>0</v>
       </c>
       <c r="P55">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q55">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="R55">
         <v>0</v>
@@ -14428,22 +14428,22 @@
         <v>245</v>
       </c>
       <c r="F56">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G56">
         <v>2.86</v>
       </c>
       <c r="H56">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="I56">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J56">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K56">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L56">
         <v>1.01</v>
@@ -14452,40 +14452,40 @@
         <v>1.01</v>
       </c>
       <c r="N56">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="O56">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P56">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q56">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R56">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S56">
         <v>3.9</v>
       </c>
       <c r="T56">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U56">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="V56">
         <v>1.41</v>
       </c>
       <c r="W56">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X56">
         <v>1000</v>
       </c>
       <c r="Y56">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z56">
         <v>29</v>
@@ -14512,7 +14512,7 @@
         <v>17.5</v>
       </c>
       <c r="AH56">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI56">
         <v>1000</v>
@@ -14521,7 +14521,7 @@
         <v>1000</v>
       </c>
       <c r="AK56">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL56">
         <v>1000</v>
@@ -14539,13 +14539,13 @@
         <v>1.96</v>
       </c>
       <c r="AQ56">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR56">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS56">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AT56">
         <v>6.2</v>
@@ -14557,7 +14557,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW56">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AX56">
         <v>10.5</v>
@@ -14569,25 +14569,25 @@
         <v>1.83</v>
       </c>
       <c r="BA56">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="BB56">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="BC56">
         <v>1.88</v>
       </c>
       <c r="BD56">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="BE56">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="BF56">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="BG56">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="BH56">
         <v>1000</v>
@@ -14676,13 +14676,13 @@
         <v>2.26</v>
       </c>
       <c r="H57">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="I57">
         <v>4.7</v>
       </c>
       <c r="J57">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K57">
         <v>3.45</v>
@@ -14703,7 +14703,7 @@
         <v>1.57</v>
       </c>
       <c r="Q57">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="R57">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>3.55</v>
       </c>
       <c r="K58">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -15160,7 +15160,7 @@
         <v>2.04</v>
       </c>
       <c r="H59">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I59">
         <v>5.5</v>
@@ -15187,7 +15187,7 @@
         <v>1.64</v>
       </c>
       <c r="Q59">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R59">
         <v>0</v>
@@ -15429,7 +15429,7 @@
         <v>1.58</v>
       </c>
       <c r="Q60">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R60">
         <v>0</v>
@@ -15504,10 +15504,10 @@
         <v>120</v>
       </c>
       <c r="AP60">
-        <v>3.35</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ60">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="AR60">
         <v>4.5</v>
@@ -15516,25 +15516,25 @@
         <v>5</v>
       </c>
       <c r="AT60">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="AU60">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="AV60">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="AW60">
         <v>4.9</v>
       </c>
       <c r="AX60">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="AY60">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="AZ60">
-        <v>4.3</v>
+        <v>19</v>
       </c>
       <c r="BA60">
         <v>5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-01.xlsx
@@ -1240,7 +1240,7 @@
     <t>Sport Boys (Per)</t>
   </si>
   <si>
-    <t>2026-07-30 18:21:09</t>
+    <t>2026-07-30 20:36:23</t>
   </si>
 </sst>
 </file>
@@ -1834,7 +1834,7 @@
         <v>283</v>
       </c>
       <c r="F2">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G2">
         <v>2.74</v>
@@ -1843,7 +1843,7 @@
         <v>2.8</v>
       </c>
       <c r="I2">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J2">
         <v>3.45</v>
@@ -1882,7 +1882,7 @@
         <v>2.18</v>
       </c>
       <c r="V2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W2">
         <v>1.57</v>
@@ -1894,7 +1894,7 @@
         <v>12</v>
       </c>
       <c r="Z2">
-        <v>28</v>
+        <v>970</v>
       </c>
       <c r="AA2">
         <v>65</v>
@@ -1909,7 +1909,7 @@
         <v>970</v>
       </c>
       <c r="AE2">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AF2">
         <v>18</v>
@@ -2005,7 +2005,7 @@
         <v>9.4</v>
       </c>
       <c r="BK2">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -2017,7 +2017,7 @@
         <v>5.7</v>
       </c>
       <c r="BO2">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BP2">
         <v>1000</v>
@@ -2041,7 +2041,7 @@
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2">
         <v>1000</v>
@@ -2076,7 +2076,7 @@
         <v>284</v>
       </c>
       <c r="F3">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G3">
         <v>3.2</v>
@@ -2085,16 +2085,16 @@
         <v>2.56</v>
       </c>
       <c r="I3">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J3">
         <v>3.2</v>
       </c>
       <c r="K3">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L3">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="M3">
         <v>1.01</v>
@@ -2106,10 +2106,10 @@
         <v>1.33</v>
       </c>
       <c r="P3">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R3">
         <v>1.28</v>
@@ -2318,22 +2318,22 @@
         <v>285</v>
       </c>
       <c r="F4">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="G4">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="H4">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I4">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -2345,13 +2345,13 @@
         <v>3.4</v>
       </c>
       <c r="O4">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P4">
         <v>1.83</v>
       </c>
       <c r="Q4">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="R4">
         <v>1.32</v>
@@ -2366,22 +2366,22 @@
         <v>2</v>
       </c>
       <c r="V4">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W4">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="X4">
         <v>16.5</v>
       </c>
       <c r="Y4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z4">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA4">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB4">
         <v>11</v>
@@ -2393,7 +2393,7 @@
         <v>21</v>
       </c>
       <c r="AE4">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF4">
         <v>15</v>
@@ -2405,7 +2405,7 @@
         <v>23</v>
       </c>
       <c r="AI4">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ4">
         <v>29</v>
@@ -2423,61 +2423,61 @@
         <v>19</v>
       </c>
       <c r="AO4">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH4">
         <v>3.85</v>
@@ -2560,7 +2560,7 @@
         <v>286</v>
       </c>
       <c r="F5">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G5">
         <v>1.6</v>
@@ -2575,10 +2575,10 @@
         <v>3.9</v>
       </c>
       <c r="K5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L5">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M5">
         <v>1.09</v>
@@ -2587,13 +2587,13 @@
         <v>3.1</v>
       </c>
       <c r="O5">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P5">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q5">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R5">
         <v>1.27</v>
@@ -2814,7 +2814,7 @@
         <v>990</v>
       </c>
       <c r="J6">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2850,10 +2850,10 @@
         <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -3074,7 +3074,7 @@
         <v>1.25</v>
       </c>
       <c r="P7">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q7">
         <v>1.74</v>
@@ -3083,13 +3083,13 @@
         <v>1.47</v>
       </c>
       <c r="S7">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="T7">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="U7">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V7">
         <v>2.3</v>
@@ -3206,40 +3206,40 @@
         <v>7.8</v>
       </c>
       <c r="BH7">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI7">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ7">
         <v>9.800000000000001</v>
       </c>
       <c r="BK7">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO7">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT7">
         <v>4.5</v>
@@ -3257,13 +3257,13 @@
         <v>24</v>
       </c>
       <c r="BY7">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BZ7">
         <v>25</v>
       </c>
       <c r="CA7">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB7" t="s">
         <v>408</v>
@@ -3298,13 +3298,13 @@
         <v>4.3</v>
       </c>
       <c r="J8">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K8">
         <v>3.85</v>
       </c>
       <c r="L8">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M8">
         <v>1.07</v>
@@ -3316,7 +3316,7 @@
         <v>1.31</v>
       </c>
       <c r="P8">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q8">
         <v>1.9</v>
@@ -3451,7 +3451,7 @@
         <v>3.55</v>
       </c>
       <c r="BI8">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="BJ8">
         <v>10</v>
@@ -3540,7 +3540,7 @@
         <v>2.48</v>
       </c>
       <c r="J9">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K9">
         <v>4.2</v>
@@ -3773,16 +3773,16 @@
         <v>2.7</v>
       </c>
       <c r="G10">
+        <v>2.8</v>
+      </c>
+      <c r="H10">
+        <v>2.78</v>
+      </c>
+      <c r="I10">
         <v>2.84</v>
       </c>
-      <c r="H10">
-        <v>2.76</v>
-      </c>
-      <c r="I10">
-        <v>2.8</v>
-      </c>
       <c r="J10">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K10">
         <v>3.65</v>
@@ -3794,82 +3794,82 @@
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O10">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P10">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q10">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R10">
         <v>1.39</v>
       </c>
       <c r="S10">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T10">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="U10">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V10">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W10">
         <v>1.55</v>
       </c>
       <c r="X10">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y10">
         <v>12.5</v>
       </c>
       <c r="Z10">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AA10">
         <v>44</v>
       </c>
       <c r="AB10">
+        <v>12.5</v>
+      </c>
+      <c r="AC10">
+        <v>8</v>
+      </c>
+      <c r="AD10">
+        <v>13</v>
+      </c>
+      <c r="AE10">
+        <v>32</v>
+      </c>
+      <c r="AF10">
+        <v>21</v>
+      </c>
+      <c r="AG10">
         <v>14</v>
-      </c>
-      <c r="AC10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD10">
-        <v>13.5</v>
-      </c>
-      <c r="AE10">
-        <v>36</v>
-      </c>
-      <c r="AF10">
-        <v>22</v>
-      </c>
-      <c r="AG10">
-        <v>14.5</v>
       </c>
       <c r="AH10">
         <v>16.5</v>
       </c>
       <c r="AI10">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ10">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL10">
         <v>42</v>
       </c>
       <c r="AM10">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN10">
         <v>25</v>
@@ -3881,25 +3881,25 @@
         <v>13</v>
       </c>
       <c r="AQ10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR10">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS10">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AT10">
         <v>11</v>
       </c>
       <c r="AU10">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW10">
-        <v>6.4</v>
+        <v>26</v>
       </c>
       <c r="AX10">
         <v>16.5</v>
@@ -3908,28 +3908,28 @@
         <v>11</v>
       </c>
       <c r="AZ10">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA10">
-        <v>6.8</v>
+        <v>34</v>
       </c>
       <c r="BB10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC10">
-        <v>6.4</v>
+        <v>26</v>
       </c>
       <c r="BD10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE10">
-        <v>7.4</v>
+        <v>65</v>
       </c>
       <c r="BF10">
         <v>20</v>
       </c>
       <c r="BG10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH10">
         <v>4.4</v>
@@ -4012,19 +4012,19 @@
         <v>292</v>
       </c>
       <c r="F11">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="G11">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H11">
         <v>2.96</v>
       </c>
       <c r="I11">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J11">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K11">
         <v>3.8</v>
@@ -4051,7 +4051,7 @@
         <v>1.48</v>
       </c>
       <c r="S11">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T11">
         <v>1.63</v>
@@ -4060,10 +4060,10 @@
         <v>2.44</v>
       </c>
       <c r="V11">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W11">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X11">
         <v>22</v>
@@ -4257,13 +4257,13 @@
         <v>1.04</v>
       </c>
       <c r="G12">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H12">
         <v>1.04</v>
       </c>
       <c r="I12">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J12">
         <v>1.04</v>
@@ -4278,13 +4278,13 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O12">
         <v>1.39</v>
       </c>
       <c r="P12">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Q12">
         <v>1.39</v>
@@ -4296,10 +4296,10 @@
         <v>1.38</v>
       </c>
       <c r="T12">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U12">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V12">
         <v>1.02</v>
@@ -4499,13 +4499,13 @@
         <v>1.04</v>
       </c>
       <c r="G13">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H13">
         <v>1.04</v>
       </c>
       <c r="I13">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J13">
         <v>1.04</v>
@@ -4538,10 +4538,10 @@
         <v>1.28</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V13">
         <v>1.02</v>
@@ -4762,13 +4762,13 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O14">
         <v>1.37</v>
       </c>
       <c r="P14">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q14">
         <v>1.37</v>
@@ -4777,7 +4777,7 @@
         <v>1.15</v>
       </c>
       <c r="S14">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="T14">
         <v>1.11</v>
@@ -4992,7 +4992,7 @@
         <v>990</v>
       </c>
       <c r="J15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K15">
         <v>950</v>
@@ -5249,13 +5249,13 @@
         <v>1.41</v>
       </c>
       <c r="O16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P16">
         <v>1.41</v>
       </c>
       <c r="Q16">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="R16">
         <v>1.18</v>
@@ -5464,7 +5464,7 @@
         <v>298</v>
       </c>
       <c r="F17">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G17">
         <v>3.85</v>
@@ -5473,16 +5473,16 @@
         <v>2.08</v>
       </c>
       <c r="I17">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J17">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K17">
         <v>4</v>
       </c>
       <c r="L17">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M17">
         <v>1.05</v>
@@ -5500,19 +5500,19 @@
         <v>1.73</v>
       </c>
       <c r="R17">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S17">
         <v>2.96</v>
       </c>
       <c r="T17">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U17">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V17">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W17">
         <v>1.35</v>
@@ -5527,7 +5527,7 @@
         <v>18</v>
       </c>
       <c r="AA17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB17">
         <v>19</v>
@@ -5605,7 +5605,7 @@
         <v>12</v>
       </c>
       <c r="BA17">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB17">
         <v>4.4</v>
@@ -5626,40 +5626,40 @@
         <v>10</v>
       </c>
       <c r="BH17">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI17">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="BJ17">
         <v>9.199999999999999</v>
       </c>
       <c r="BK17">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN17">
         <v>7</v>
       </c>
       <c r="BO17">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP17">
         <v>27</v>
       </c>
       <c r="BQ17">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BR17">
         <v>36</v>
       </c>
       <c r="BS17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT17">
         <v>5.2</v>
@@ -5671,19 +5671,19 @@
         <v>15</v>
       </c>
       <c r="BW17">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY17">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ17">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA17">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB17" t="s">
         <v>408</v>
@@ -5718,16 +5718,16 @@
         <v>3.05</v>
       </c>
       <c r="J18">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K18">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L18">
         <v>1.36</v>
       </c>
       <c r="M18">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N18">
         <v>3.3</v>
@@ -5736,7 +5736,7 @@
         <v>1.35</v>
       </c>
       <c r="P18">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q18">
         <v>2.02</v>
@@ -5745,10 +5745,10 @@
         <v>1.3</v>
       </c>
       <c r="S18">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T18">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U18">
         <v>2.06</v>
@@ -5763,16 +5763,16 @@
         <v>15.5</v>
       </c>
       <c r="Y18">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z18">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA18">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB18">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AC18">
         <v>9.199999999999999</v>
@@ -5802,10 +5802,10 @@
         <v>40</v>
       </c>
       <c r="AL18">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM18">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN18">
         <v>32</v>
@@ -5823,7 +5823,7 @@
         <v>16</v>
       </c>
       <c r="AS18">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AT18">
         <v>9.199999999999999</v>
@@ -5835,7 +5835,7 @@
         <v>11</v>
       </c>
       <c r="AW18">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AX18">
         <v>15.5</v>
@@ -5859,7 +5859,7 @@
         <v>32</v>
       </c>
       <c r="BE18">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BF18">
         <v>22</v>
@@ -5868,22 +5868,22 @@
         <v>23</v>
       </c>
       <c r="BH18">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI18">
         <v>2.62</v>
       </c>
       <c r="BJ18">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK18">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN18">
         <v>5.9</v>
@@ -5895,16 +5895,16 @@
         <v>23</v>
       </c>
       <c r="BQ18">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT18">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU18">
         <v>4.4</v>
@@ -5913,19 +5913,19 @@
         <v>32</v>
       </c>
       <c r="BW18">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB18" t="s">
         <v>408</v>
@@ -5948,13 +5948,13 @@
         <v>300</v>
       </c>
       <c r="F19">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G19">
         <v>2.82</v>
       </c>
       <c r="H19">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I19">
         <v>3.15</v>
@@ -5963,10 +5963,10 @@
         <v>3.3</v>
       </c>
       <c r="K19">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L19">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M19">
         <v>1.07</v>
@@ -5975,13 +5975,13 @@
         <v>3.6</v>
       </c>
       <c r="O19">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P19">
         <v>1.89</v>
       </c>
       <c r="Q19">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R19">
         <v>1.34</v>
@@ -5990,10 +5990,10 @@
         <v>3.4</v>
       </c>
       <c r="T19">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="U19">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V19">
         <v>1.46</v>
@@ -6113,7 +6113,7 @@
         <v>3.5</v>
       </c>
       <c r="BI19">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BJ19">
         <v>9.6</v>
@@ -6149,7 +6149,7 @@
         <v>6.2</v>
       </c>
       <c r="BU19">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV19">
         <v>23</v>
@@ -6190,13 +6190,13 @@
         <v>301</v>
       </c>
       <c r="F20">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G20">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H20">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I20">
         <v>4.2</v>
@@ -6220,10 +6220,10 @@
         <v>1.42</v>
       </c>
       <c r="P20">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q20">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R20">
         <v>1.27</v>
@@ -6232,7 +6232,7 @@
         <v>4.2</v>
       </c>
       <c r="T20">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U20">
         <v>1.94</v>
@@ -6274,7 +6274,7 @@
         <v>11.5</v>
       </c>
       <c r="AH20">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI20">
         <v>70</v>
@@ -6307,7 +6307,7 @@
         <v>21</v>
       </c>
       <c r="AS20">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT20">
         <v>7.2</v>
@@ -6319,7 +6319,7 @@
         <v>14.5</v>
       </c>
       <c r="AW20">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX20">
         <v>11.5</v>
@@ -6331,10 +6331,10 @@
         <v>17.5</v>
       </c>
       <c r="BA20">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB20">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC20">
         <v>20</v>
@@ -6343,13 +6343,13 @@
         <v>34</v>
       </c>
       <c r="BE20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF20">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BG20">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH20">
         <v>3.05</v>
@@ -6361,22 +6361,22 @@
         <v>10.5</v>
       </c>
       <c r="BK20">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN20">
         <v>4.9</v>
       </c>
       <c r="BO20">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BP20">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ20">
         <v>8</v>
@@ -6403,10 +6403,10 @@
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ20">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
         <v>10.5</v>
@@ -6441,7 +6441,7 @@
         <v>2.88</v>
       </c>
       <c r="I21">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J21">
         <v>3.25</v>
@@ -6456,16 +6456,16 @@
         <v>1.07</v>
       </c>
       <c r="N21">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O21">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P21">
         <v>1.93</v>
       </c>
       <c r="Q21">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R21">
         <v>1.37</v>
@@ -6480,7 +6480,7 @@
         <v>2.2</v>
       </c>
       <c r="V21">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W21">
         <v>1.54</v>
@@ -6507,7 +6507,7 @@
         <v>15</v>
       </c>
       <c r="AE21">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF21">
         <v>19.5</v>
@@ -6531,7 +6531,7 @@
         <v>46</v>
       </c>
       <c r="AM21">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN21">
         <v>25</v>
@@ -6549,7 +6549,7 @@
         <v>17</v>
       </c>
       <c r="AS21">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT21">
         <v>10</v>
@@ -6573,25 +6573,25 @@
         <v>14</v>
       </c>
       <c r="BA21">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB21">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC21">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD21">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE21">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF21">
         <v>20</v>
       </c>
       <c r="BG21">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH21">
         <v>3.5</v>
@@ -6609,7 +6609,7 @@
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN21">
         <v>5.9</v>
@@ -6639,7 +6639,7 @@
         <v>23</v>
       </c>
       <c r="BW21">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX21">
         <v>36</v>
@@ -6648,7 +6648,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BZ21">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CA21">
         <v>7.8</v>
@@ -6689,31 +6689,31 @@
         <v>4.1</v>
       </c>
       <c r="K22">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M22">
         <v>1.09</v>
       </c>
       <c r="N22">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O22">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P22">
         <v>1.72</v>
       </c>
       <c r="Q22">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R22">
         <v>1.27</v>
       </c>
       <c r="S22">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T22">
         <v>2.3</v>
@@ -6737,10 +6737,10 @@
         <v>70</v>
       </c>
       <c r="AA22">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AB22">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC22">
         <v>9.800000000000001</v>
@@ -6788,22 +6788,22 @@
         <v>16</v>
       </c>
       <c r="AR22">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AS22">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT22">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU22">
         <v>8.6</v>
       </c>
       <c r="AV22">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AW22">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX22">
         <v>7.2</v>
@@ -6812,10 +6812,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ22">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BA22">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BB22">
         <v>12.5</v>
@@ -6824,16 +6824,16 @@
         <v>17.5</v>
       </c>
       <c r="BD22">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE22">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF22">
         <v>10</v>
       </c>
       <c r="BG22">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6928,7 +6928,7 @@
         <v>1.74</v>
       </c>
       <c r="J23">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K23">
         <v>4.4</v>
@@ -6940,13 +6940,13 @@
         <v>1.06</v>
       </c>
       <c r="N23">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O23">
         <v>1.31</v>
       </c>
       <c r="P23">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="Q23">
         <v>1.92</v>
@@ -7081,7 +7081,7 @@
         <v>3.65</v>
       </c>
       <c r="BI23">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ23">
         <v>11</v>
@@ -7161,10 +7161,10 @@
         <v>2.5</v>
       </c>
       <c r="G24">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="H24">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I24">
         <v>2.92</v>
@@ -7188,7 +7188,7 @@
         <v>1.22</v>
       </c>
       <c r="P24">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q24">
         <v>1.63</v>
@@ -7203,13 +7203,13 @@
         <v>1.58</v>
       </c>
       <c r="U24">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V24">
         <v>1.52</v>
       </c>
       <c r="W24">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X24">
         <v>950</v>
@@ -7218,7 +7218,7 @@
         <v>15</v>
       </c>
       <c r="Z24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA24">
         <v>46</v>
@@ -7233,7 +7233,7 @@
         <v>13</v>
       </c>
       <c r="AE24">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF24">
         <v>20</v>
@@ -7251,16 +7251,16 @@
         <v>38</v>
       </c>
       <c r="AK24">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL24">
         <v>34</v>
       </c>
       <c r="AM24">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN24">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO24">
         <v>25</v>
@@ -7272,10 +7272,10 @@
         <v>12.5</v>
       </c>
       <c r="AR24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS24">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="AT24">
         <v>12</v>
@@ -7287,7 +7287,7 @@
         <v>11</v>
       </c>
       <c r="AW24">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX24">
         <v>16.5</v>
@@ -7299,19 +7299,19 @@
         <v>13</v>
       </c>
       <c r="BA24">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="BB24">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="BC24">
         <v>21</v>
       </c>
       <c r="BD24">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE24">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF24">
         <v>14</v>
@@ -7320,22 +7320,22 @@
         <v>16</v>
       </c>
       <c r="BH24">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI24">
         <v>3.15</v>
       </c>
       <c r="BJ24">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK24">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BN24">
         <v>6</v>
@@ -7347,37 +7347,37 @@
         <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT24">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU24">
         <v>4.6</v>
       </c>
       <c r="BV24">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW24">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
+        <v>9.4</v>
+      </c>
+      <c r="BZ24">
+        <v>1000</v>
+      </c>
+      <c r="CA24">
         <v>8</v>
-      </c>
-      <c r="BZ24">
-        <v>1000</v>
-      </c>
-      <c r="CA24">
-        <v>7</v>
       </c>
       <c r="CB24" t="s">
         <v>408</v>
@@ -7409,19 +7409,19 @@
         <v>2.42</v>
       </c>
       <c r="I25">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J25">
         <v>3.65</v>
       </c>
       <c r="K25">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L25">
         <v>1.27</v>
       </c>
       <c r="M25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N25">
         <v>4.6</v>
@@ -7439,7 +7439,7 @@
         <v>1.49</v>
       </c>
       <c r="S25">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T25">
         <v>1.58</v>
@@ -7666,13 +7666,13 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="O26">
         <v>1.15</v>
       </c>
       <c r="P26">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q26">
         <v>1.15</v>
@@ -7908,13 +7908,13 @@
         <v>1.01</v>
       </c>
       <c r="N27">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="O27">
         <v>1.17</v>
       </c>
       <c r="P27">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q27">
         <v>1.16</v>
@@ -8156,7 +8156,7 @@
         <v>1.22</v>
       </c>
       <c r="P28">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q28">
         <v>1.65</v>
@@ -8383,7 +8383,7 @@
         <v>4.9</v>
       </c>
       <c r="K29">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -8413,7 +8413,7 @@
         <v>1.46</v>
       </c>
       <c r="U29">
-        <v>2.7</v>
+        <v>1.11</v>
       </c>
       <c r="V29">
         <v>1.21</v>
@@ -8610,7 +8610,7 @@
         <v>311</v>
       </c>
       <c r="F30">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="G30">
         <v>1.97</v>
@@ -8619,46 +8619,46 @@
         <v>3.7</v>
       </c>
       <c r="I30">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J30">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K30">
         <v>4.5</v>
       </c>
       <c r="L30">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M30">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N30">
         <v>7.6</v>
       </c>
       <c r="O30">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P30">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q30">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R30">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S30">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="T30">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="U30">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="V30">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W30">
         <v>2.02</v>
@@ -8667,22 +8667,22 @@
         <v>40</v>
       </c>
       <c r="Y30">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z30">
         <v>40</v>
       </c>
       <c r="AA30">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB30">
         <v>21</v>
       </c>
       <c r="AC30">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD30">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE30">
         <v>38</v>
@@ -8697,13 +8697,13 @@
         <v>15</v>
       </c>
       <c r="AI30">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ30">
         <v>25</v>
       </c>
       <c r="AK30">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL30">
         <v>23</v>
@@ -8715,43 +8715,43 @@
         <v>6.6</v>
       </c>
       <c r="AO30">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP30">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="AQ30">
-        <v>7.2</v>
+        <v>18.5</v>
       </c>
       <c r="AR30">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="AS30">
-        <v>8.4</v>
+        <v>34</v>
       </c>
       <c r="AT30">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU30">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AV30">
         <v>15</v>
       </c>
       <c r="AW30">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="AX30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY30">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ30">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA30">
-        <v>7.4</v>
+        <v>19.5</v>
       </c>
       <c r="BB30">
         <v>21</v>
@@ -8763,10 +8763,10 @@
         <v>19</v>
       </c>
       <c r="BE30">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="BF30">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BG30">
         <v>16</v>
@@ -9106,7 +9106,7 @@
         <v>990</v>
       </c>
       <c r="J32">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K32">
         <v>950</v>
@@ -9127,7 +9127,7 @@
         <v>1.25</v>
       </c>
       <c r="Q32">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="R32">
         <v>1.25</v>
@@ -9363,10 +9363,10 @@
         <v>4.8</v>
       </c>
       <c r="O33">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P33">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q33">
         <v>1.68</v>
@@ -9507,7 +9507,7 @@
         <v>10</v>
       </c>
       <c r="BK33">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL33">
         <v>1000</v>
@@ -9531,16 +9531,16 @@
         <v>22</v>
       </c>
       <c r="BS33">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT33">
         <v>10</v>
       </c>
       <c r="BU33">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV33">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW33">
         <v>12.5</v>
@@ -9578,10 +9578,10 @@
         <v>315</v>
       </c>
       <c r="F34">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G34">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="H34">
         <v>8.199999999999999</v>
@@ -9599,7 +9599,7 @@
         <v>1.21</v>
       </c>
       <c r="M34">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N34">
         <v>6.6</v>
@@ -9611,7 +9611,7 @@
         <v>2.94</v>
       </c>
       <c r="Q34">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R34">
         <v>1.81</v>
@@ -9629,7 +9629,7 @@
         <v>1.11</v>
       </c>
       <c r="W34">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="X34">
         <v>40</v>
@@ -9638,28 +9638,28 @@
         <v>44</v>
       </c>
       <c r="Z34">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AA34">
         <v>270</v>
       </c>
       <c r="AB34">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC34">
         <v>16.5</v>
       </c>
       <c r="AD34">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE34">
         <v>120</v>
       </c>
       <c r="AF34">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG34">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH34">
         <v>25</v>
@@ -9680,22 +9680,22 @@
         <v>90</v>
       </c>
       <c r="AN34">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AO34">
         <v>110</v>
       </c>
       <c r="AP34">
-        <v>26</v>
+        <v>6.6</v>
       </c>
       <c r="AQ34">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AR34">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS34">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT34">
         <v>10</v>
@@ -9704,22 +9704,22 @@
         <v>12</v>
       </c>
       <c r="AV34">
-        <v>24</v>
+        <v>6.6</v>
       </c>
       <c r="AW34">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX34">
         <v>8.6</v>
       </c>
       <c r="AY34">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ34">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA34">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB34">
         <v>10</v>
@@ -9728,16 +9728,16 @@
         <v>10.5</v>
       </c>
       <c r="BD34">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE34">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF34">
         <v>3.45</v>
       </c>
       <c r="BG34">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9749,7 +9749,7 @@
         <v>14.5</v>
       </c>
       <c r="BK34">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BL34">
         <v>1000</v>
@@ -9758,34 +9758,34 @@
         <v>2.16</v>
       </c>
       <c r="BN34">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO34">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BP34">
         <v>10.5</v>
       </c>
       <c r="BQ34">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BR34">
         <v>25</v>
       </c>
       <c r="BS34">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="BT34">
         <v>17.5</v>
       </c>
       <c r="BU34">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="BV34">
         <v>1000</v>
       </c>
       <c r="BW34">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BX34">
         <v>1000</v>
@@ -9797,7 +9797,7 @@
         <v>12.5</v>
       </c>
       <c r="CA34">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CB34" t="s">
         <v>408</v>
@@ -9853,7 +9853,7 @@
         <v>2.04</v>
       </c>
       <c r="Q35">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="R35">
         <v>1.4</v>
@@ -10346,10 +10346,10 @@
         <v>3.95</v>
       </c>
       <c r="T37">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U37">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V37">
         <v>1.53</v>
@@ -10579,7 +10579,7 @@
         <v>1.26</v>
       </c>
       <c r="Q38">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="R38">
         <v>1.18</v>
@@ -10791,7 +10791,7 @@
         <v>2.46</v>
       </c>
       <c r="G39">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H39">
         <v>2.88</v>
@@ -10809,7 +10809,7 @@
         <v>1.29</v>
       </c>
       <c r="M39">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N39">
         <v>3.7</v>
@@ -10824,7 +10824,7 @@
         <v>1.89</v>
       </c>
       <c r="R39">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S39">
         <v>3.25</v>
@@ -11317,7 +11317,7 @@
         <v>2.02</v>
       </c>
       <c r="U41">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V41">
         <v>1.26</v>
@@ -11580,7 +11580,7 @@
         <v>1000</v>
       </c>
       <c r="AB42">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC42">
         <v>20</v>
@@ -11592,10 +11592,10 @@
         <v>1000</v>
       </c>
       <c r="AF42">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG42">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH42">
         <v>1000</v>
@@ -11607,7 +11607,7 @@
         <v>12.5</v>
       </c>
       <c r="AK42">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL42">
         <v>1000</v>
@@ -11622,58 +11622,58 @@
         <v>1000</v>
       </c>
       <c r="AP42">
-        <v>1.34</v>
+        <v>2.36</v>
       </c>
       <c r="AQ42">
-        <v>1.34</v>
+        <v>2.36</v>
       </c>
       <c r="AR42">
-        <v>1.34</v>
+        <v>2.36</v>
       </c>
       <c r="AS42">
-        <v>1.34</v>
+        <v>2.36</v>
       </c>
       <c r="AT42">
-        <v>1.34</v>
+        <v>4.5</v>
       </c>
       <c r="AU42">
-        <v>1.26</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV42">
-        <v>1.34</v>
+        <v>2.36</v>
       </c>
       <c r="AW42">
-        <v>1.34</v>
+        <v>2.36</v>
       </c>
       <c r="AX42">
-        <v>1.34</v>
+        <v>4.6</v>
       </c>
       <c r="AY42">
-        <v>1.34</v>
+        <v>7.6</v>
       </c>
       <c r="AZ42">
-        <v>1.34</v>
+        <v>2.36</v>
       </c>
       <c r="BA42">
-        <v>1.34</v>
+        <v>2.36</v>
       </c>
       <c r="BB42">
-        <v>1.21</v>
+        <v>5.8</v>
       </c>
       <c r="BC42">
-        <v>1.34</v>
+        <v>11</v>
       </c>
       <c r="BD42">
-        <v>1.34</v>
+        <v>2.36</v>
       </c>
       <c r="BE42">
-        <v>1.34</v>
+        <v>2.36</v>
       </c>
       <c r="BF42">
-        <v>1.15</v>
+        <v>4.5</v>
       </c>
       <c r="BG42">
-        <v>1.34</v>
+        <v>2.36</v>
       </c>
       <c r="BH42">
         <v>4.4</v>
@@ -12028,7 +12028,7 @@
         <v>1.19</v>
       </c>
       <c r="P44">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q44">
         <v>1.57</v>
@@ -12037,13 +12037,13 @@
         <v>1.63</v>
       </c>
       <c r="S44">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T44">
         <v>1.59</v>
       </c>
       <c r="U44">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V44">
         <v>1.29</v>
@@ -12055,7 +12055,7 @@
         <v>32</v>
       </c>
       <c r="Y44">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Z44">
         <v>44</v>
@@ -12070,7 +12070,7 @@
         <v>12</v>
       </c>
       <c r="AD44">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AE44">
         <v>55</v>
@@ -12091,7 +12091,7 @@
         <v>25</v>
       </c>
       <c r="AK44">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AL44">
         <v>32</v>
@@ -12112,10 +12112,10 @@
         <v>16.5</v>
       </c>
       <c r="AR44">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AS44">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AT44">
         <v>9.800000000000001</v>
@@ -12127,7 +12127,7 @@
         <v>13</v>
       </c>
       <c r="AW44">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AX44">
         <v>10.5</v>
@@ -12139,7 +12139,7 @@
         <v>14</v>
       </c>
       <c r="BA44">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BB44">
         <v>15</v>
@@ -12151,13 +12151,13 @@
         <v>18.5</v>
       </c>
       <c r="BE44">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BF44">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="BG44">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BH44">
         <v>1000</v>
@@ -12542,19 +12542,19 @@
         <v>1000</v>
       </c>
       <c r="Z46">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA46">
         <v>1000</v>
       </c>
       <c r="AB46">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC46">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD46">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE46">
         <v>1000</v>
@@ -12563,85 +12563,85 @@
         <v>1000</v>
       </c>
       <c r="AG46">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH46">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI46">
         <v>1000</v>
       </c>
       <c r="AJ46">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK46">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL46">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM46">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN46">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO46">
         <v>1000</v>
       </c>
       <c r="AP46">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="AQ46">
-        <v>1.06</v>
+        <v>2.86</v>
       </c>
       <c r="AR46">
-        <v>1.06</v>
+        <v>2.66</v>
       </c>
       <c r="AS46">
-        <v>1.06</v>
+        <v>2.86</v>
       </c>
       <c r="AT46">
-        <v>1.06</v>
+        <v>2.28</v>
       </c>
       <c r="AU46">
-        <v>1.06</v>
+        <v>2.26</v>
       </c>
       <c r="AV46">
-        <v>1.06</v>
+        <v>2.5</v>
       </c>
       <c r="AW46">
-        <v>1.06</v>
+        <v>2.86</v>
       </c>
       <c r="AX46">
-        <v>1.06</v>
+        <v>2.86</v>
       </c>
       <c r="AY46">
-        <v>1.06</v>
+        <v>2.28</v>
       </c>
       <c r="AZ46">
-        <v>1.06</v>
+        <v>2.5</v>
       </c>
       <c r="BA46">
-        <v>1.06</v>
+        <v>2.86</v>
       </c>
       <c r="BB46">
-        <v>1.06</v>
+        <v>2.52</v>
       </c>
       <c r="BC46">
-        <v>1.06</v>
+        <v>2.5</v>
       </c>
       <c r="BD46">
-        <v>1.06</v>
+        <v>2.64</v>
       </c>
       <c r="BE46">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="BF46">
-        <v>1.06</v>
+        <v>7.4</v>
       </c>
       <c r="BG46">
-        <v>1.06</v>
+        <v>2.86</v>
       </c>
       <c r="BH46">
         <v>1000</v>
@@ -12671,13 +12671,13 @@
         <v>16</v>
       </c>
       <c r="BQ46">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BR46">
         <v>32</v>
       </c>
       <c r="BS46">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BT46">
         <v>11.5</v>
@@ -12689,16 +12689,16 @@
         <v>50</v>
       </c>
       <c r="BW46">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="BX46">
         <v>1000</v>
       </c>
       <c r="BY46">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BZ46">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA46">
         <v>1.84</v>
@@ -12739,7 +12739,7 @@
         <v>3.5</v>
       </c>
       <c r="K47">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L47">
         <v>1.01</v>
@@ -12760,13 +12760,13 @@
         <v>2.02</v>
       </c>
       <c r="R47">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S47">
         <v>3.75</v>
       </c>
       <c r="T47">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="U47">
         <v>2</v>
@@ -12781,7 +12781,7 @@
         <v>14.5</v>
       </c>
       <c r="Y47">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Z47">
         <v>15.5</v>
@@ -12841,13 +12841,13 @@
         <v>12</v>
       </c>
       <c r="AS47">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT47">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU47">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV47">
         <v>8.4</v>
@@ -12859,28 +12859,28 @@
         <v>19.5</v>
       </c>
       <c r="AY47">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ47">
         <v>16.5</v>
       </c>
       <c r="BA47">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB47">
+        <v>6</v>
+      </c>
+      <c r="BC47">
         <v>5.9</v>
       </c>
-      <c r="BC47">
-        <v>5.7</v>
-      </c>
       <c r="BD47">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE47">
         <v>6.2</v>
       </c>
       <c r="BF47">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG47">
         <v>18</v>
@@ -12969,16 +12969,16 @@
         <v>1.74</v>
       </c>
       <c r="G48">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H48">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I48">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J48">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K48">
         <v>4.7</v>
@@ -12990,13 +12990,13 @@
         <v>1.03</v>
       </c>
       <c r="N48">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O48">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P48">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="Q48">
         <v>1.56</v>
@@ -13008,121 +13008,121 @@
         <v>2.4</v>
       </c>
       <c r="T48">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U48">
         <v>2.42</v>
       </c>
       <c r="V48">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W48">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X48">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y48">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="Z48">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA48">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB48">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AC48">
+        <v>11</v>
+      </c>
+      <c r="AD48">
+        <v>23</v>
+      </c>
+      <c r="AE48">
+        <v>60</v>
+      </c>
+      <c r="AF48">
+        <v>14</v>
+      </c>
+      <c r="AG48">
+        <v>11</v>
+      </c>
+      <c r="AH48">
+        <v>17</v>
+      </c>
+      <c r="AI48">
+        <v>55</v>
+      </c>
+      <c r="AJ48">
+        <v>21</v>
+      </c>
+      <c r="AK48">
+        <v>17.5</v>
+      </c>
+      <c r="AL48">
+        <v>27</v>
+      </c>
+      <c r="AM48">
+        <v>65</v>
+      </c>
+      <c r="AN48">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO48">
+        <v>44</v>
+      </c>
+      <c r="AP48">
+        <v>18</v>
+      </c>
+      <c r="AQ48">
+        <v>16.5</v>
+      </c>
+      <c r="AR48">
+        <v>1.01</v>
+      </c>
+      <c r="AS48">
+        <v>1.01</v>
+      </c>
+      <c r="AT48">
+        <v>9.4</v>
+      </c>
+      <c r="AU48">
+        <v>7.8</v>
+      </c>
+      <c r="AV48">
+        <v>13.5</v>
+      </c>
+      <c r="AW48">
+        <v>1.01</v>
+      </c>
+      <c r="AX48">
+        <v>10</v>
+      </c>
+      <c r="AY48">
+        <v>7.8</v>
+      </c>
+      <c r="AZ48">
         <v>12</v>
       </c>
-      <c r="AD48">
-        <v>22</v>
-      </c>
-      <c r="AE48">
-        <v>1000</v>
-      </c>
-      <c r="AF48">
-        <v>16.5</v>
-      </c>
-      <c r="AG48">
-        <v>12.5</v>
-      </c>
-      <c r="AH48">
-        <v>23</v>
-      </c>
-      <c r="AI48">
-        <v>1000</v>
-      </c>
-      <c r="AJ48">
-        <v>25</v>
-      </c>
-      <c r="AK48">
-        <v>21</v>
-      </c>
-      <c r="AL48">
-        <v>30</v>
-      </c>
-      <c r="AM48">
-        <v>1000</v>
-      </c>
-      <c r="AN48">
-        <v>1000</v>
-      </c>
-      <c r="AO48">
-        <v>1000</v>
-      </c>
-      <c r="AP48">
-        <v>1.03</v>
-      </c>
-      <c r="AQ48">
-        <v>14</v>
-      </c>
-      <c r="AR48">
-        <v>1.03</v>
-      </c>
-      <c r="AS48">
-        <v>1.03</v>
-      </c>
-      <c r="AT48">
-        <v>1.01</v>
-      </c>
-      <c r="AU48">
-        <v>1.01</v>
-      </c>
-      <c r="AV48">
-        <v>11.5</v>
-      </c>
-      <c r="AW48">
-        <v>1.03</v>
-      </c>
-      <c r="AX48">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY48">
-        <v>1.01</v>
-      </c>
-      <c r="AZ48">
-        <v>10.5</v>
-      </c>
       <c r="BA48">
-        <v>1.03</v>
+        <v>29</v>
       </c>
       <c r="BB48">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC48">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD48">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BE48">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF48">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BG48">
         <v>1.01</v>
@@ -13137,34 +13137,34 @@
         <v>13</v>
       </c>
       <c r="BK48">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BL48">
         <v>1000</v>
       </c>
       <c r="BM48">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BN48">
         <v>7</v>
       </c>
       <c r="BO48">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="BP48">
         <v>17.5</v>
       </c>
       <c r="BQ48">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BR48">
         <v>30</v>
       </c>
       <c r="BS48">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BT48">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BU48">
         <v>2.3</v>
@@ -13173,13 +13173,13 @@
         <v>44</v>
       </c>
       <c r="BW48">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="BX48">
         <v>50</v>
       </c>
       <c r="BY48">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="BZ48">
         <v>0</v>
@@ -13211,13 +13211,13 @@
         <v>1.04</v>
       </c>
       <c r="G49">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H49">
         <v>1.04</v>
       </c>
       <c r="I49">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J49">
         <v>1.04</v>
@@ -13232,7 +13232,7 @@
         <v>1.01</v>
       </c>
       <c r="N49">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O49">
         <v>1.15</v>
@@ -13250,13 +13250,13 @@
         <v>1.14</v>
       </c>
       <c r="T49">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U49">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V49">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W49">
         <v>1.02</v>
@@ -13695,7 +13695,7 @@
         <v>1.69</v>
       </c>
       <c r="G51">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H51">
         <v>1.04</v>
@@ -13734,16 +13734,16 @@
         <v>1.09</v>
       </c>
       <c r="T51">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U51">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V51">
         <v>1.66</v>
       </c>
       <c r="W51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X51">
         <v>1000</v>
@@ -13958,13 +13958,13 @@
         <v>1.01</v>
       </c>
       <c r="N52">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O52">
         <v>1.17</v>
       </c>
       <c r="P52">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q52">
         <v>1.16</v>
@@ -14179,13 +14179,13 @@
         <v>1.04</v>
       </c>
       <c r="G53">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H53">
         <v>1.04</v>
       </c>
       <c r="I53">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J53">
         <v>1.04</v>
@@ -14200,13 +14200,13 @@
         <v>1.01</v>
       </c>
       <c r="N53">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="O53">
         <v>1.16</v>
       </c>
       <c r="P53">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q53">
         <v>1.16</v>
@@ -14218,10 +14218,10 @@
         <v>1.16</v>
       </c>
       <c r="T53">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U53">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V53">
         <v>1.02</v>
@@ -14660,7 +14660,7 @@
         <v>336</v>
       </c>
       <c r="F55">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G55">
         <v>2.2</v>
@@ -14675,10 +14675,10 @@
         <v>3.6</v>
       </c>
       <c r="K55">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L55">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="M55">
         <v>1.06</v>
@@ -14687,19 +14687,19 @@
         <v>4.1</v>
       </c>
       <c r="O55">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P55">
         <v>2.06</v>
       </c>
       <c r="Q55">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="R55">
         <v>1.42</v>
       </c>
       <c r="S55">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T55">
         <v>1.7</v>
@@ -14717,7 +14717,7 @@
         <v>19.5</v>
       </c>
       <c r="Y55">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Z55">
         <v>34</v>
@@ -14738,7 +14738,7 @@
         <v>50</v>
       </c>
       <c r="AF55">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG55">
         <v>12.5</v>
@@ -14753,7 +14753,7 @@
         <v>30</v>
       </c>
       <c r="AK55">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL55">
         <v>40</v>
@@ -14771,13 +14771,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ55">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AR55">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AS55">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AT55">
         <v>9.4</v>
@@ -14789,37 +14789,37 @@
         <v>13.5</v>
       </c>
       <c r="AW55">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX55">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY55">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ55">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BA55">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BB55">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BC55">
         <v>18.5</v>
       </c>
       <c r="BD55">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BE55">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BF55">
         <v>10.5</v>
       </c>
       <c r="BG55">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH55">
         <v>4.6</v>
@@ -14929,7 +14929,7 @@
         <v>3.6</v>
       </c>
       <c r="O56">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="P56">
         <v>1.76</v>
@@ -15162,7 +15162,7 @@
         <v>3.95</v>
       </c>
       <c r="L57">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M57">
         <v>1.06</v>
@@ -15240,7 +15240,7 @@
         <v>46</v>
       </c>
       <c r="AL57">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM57">
         <v>100</v>
@@ -15255,28 +15255,28 @@
         <v>4.1</v>
       </c>
       <c r="AQ57">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AR57">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS57">
         <v>4.6</v>
       </c>
       <c r="AT57">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AU57">
         <v>3.3</v>
       </c>
       <c r="AV57">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AW57">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX57">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY57">
         <v>4</v>
@@ -15291,7 +15291,7 @@
         <v>4.9</v>
       </c>
       <c r="BC57">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD57">
         <v>4.8</v>
@@ -15386,10 +15386,10 @@
         <v>339</v>
       </c>
       <c r="F58">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G58">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H58">
         <v>3.65</v>
@@ -15398,7 +15398,7 @@
         <v>4.5</v>
       </c>
       <c r="J58">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K58">
         <v>4.1</v>
@@ -15422,7 +15422,7 @@
         <v>1.8</v>
       </c>
       <c r="R58">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S58">
         <v>2.6</v>
@@ -15437,7 +15437,7 @@
         <v>1.28</v>
       </c>
       <c r="W58">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X58">
         <v>22</v>
@@ -15494,58 +15494,58 @@
         <v>55</v>
       </c>
       <c r="AP58">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AQ58">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AR58">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS58">
+        <v>7</v>
+      </c>
+      <c r="AT58">
+        <v>4.5</v>
+      </c>
+      <c r="AU58">
+        <v>4.1</v>
+      </c>
+      <c r="AV58">
+        <v>5.2</v>
+      </c>
+      <c r="AW58">
         <v>6.6</v>
       </c>
-      <c r="AT58">
+      <c r="AX58">
+        <v>4.9</v>
+      </c>
+      <c r="AY58">
         <v>4.4</v>
       </c>
-      <c r="AU58">
-        <v>4</v>
-      </c>
-      <c r="AV58">
-        <v>5.1</v>
-      </c>
-      <c r="AW58">
+      <c r="AZ58">
+        <v>5.3</v>
+      </c>
+      <c r="BA58">
+        <v>6.6</v>
+      </c>
+      <c r="BB58">
+        <v>5.7</v>
+      </c>
+      <c r="BC58">
+        <v>5.5</v>
+      </c>
+      <c r="BD58">
+        <v>6.2</v>
+      </c>
+      <c r="BE58">
+        <v>7</v>
+      </c>
+      <c r="BF58">
+        <v>4.7</v>
+      </c>
+      <c r="BG58">
         <v>6.4</v>
-      </c>
-      <c r="AX58">
-        <v>4.7</v>
-      </c>
-      <c r="AY58">
-        <v>4.3</v>
-      </c>
-      <c r="AZ58">
-        <v>5.1</v>
-      </c>
-      <c r="BA58">
-        <v>6.2</v>
-      </c>
-      <c r="BB58">
-        <v>5.5</v>
-      </c>
-      <c r="BC58">
-        <v>5.3</v>
-      </c>
-      <c r="BD58">
-        <v>6</v>
-      </c>
-      <c r="BE58">
-        <v>6.6</v>
-      </c>
-      <c r="BF58">
-        <v>4.5</v>
-      </c>
-      <c r="BG58">
-        <v>6.2</v>
       </c>
       <c r="BH58">
         <v>4.7</v>
@@ -15873,13 +15873,13 @@
         <v>1.04</v>
       </c>
       <c r="G60">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H60">
         <v>1.04</v>
       </c>
       <c r="I60">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J60">
         <v>1.04</v>
@@ -15894,34 +15894,34 @@
         <v>1.01</v>
       </c>
       <c r="N60">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="O60">
         <v>1.28</v>
       </c>
       <c r="P60">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Q60">
         <v>1.28</v>
       </c>
       <c r="R60">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="S60">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T60">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U60">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V60">
         <v>1.02</v>
       </c>
       <c r="W60">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X60">
         <v>1000</v>
@@ -16136,10 +16136,10 @@
         <v>1.01</v>
       </c>
       <c r="N61">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O61">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="P61">
         <v>2.08</v>
@@ -16154,10 +16154,10 @@
         <v>2.46</v>
       </c>
       <c r="T61">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U61">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V61">
         <v>1.45</v>
@@ -16384,16 +16384,16 @@
         <v>1.31</v>
       </c>
       <c r="P62">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="Q62">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R62">
         <v>1.05</v>
       </c>
       <c r="S62">
-        <v>1.3</v>
+        <v>2.06</v>
       </c>
       <c r="T62">
         <v>1.11</v>
@@ -16602,13 +16602,13 @@
         <v>14</v>
       </c>
       <c r="H63">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I63">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J63">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K63">
         <v>950</v>
@@ -16620,34 +16620,34 @@
         <v>1.01</v>
       </c>
       <c r="N63">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="O63">
         <v>1.22</v>
       </c>
       <c r="P63">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Q63">
         <v>1.22</v>
       </c>
       <c r="R63">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="S63">
         <v>1.22</v>
       </c>
       <c r="T63">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U63">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V63">
         <v>1.01</v>
       </c>
       <c r="W63">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X63">
         <v>1000</v>
@@ -16868,10 +16868,10 @@
         <v>1.28</v>
       </c>
       <c r="P64">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q64">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R64">
         <v>1.25</v>
@@ -17104,28 +17104,28 @@
         <v>1.01</v>
       </c>
       <c r="N65">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="O65">
         <v>1.11</v>
       </c>
       <c r="P65">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="Q65">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="R65">
         <v>1.78</v>
       </c>
       <c r="S65">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="T65">
         <v>1.38</v>
       </c>
       <c r="U65">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V65">
         <v>2.08</v>
@@ -17606,10 +17606,10 @@
         <v>3.2</v>
       </c>
       <c r="T67">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U67">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V67">
         <v>1.1</v>
@@ -18072,7 +18072,7 @@
         <v>1.1</v>
       </c>
       <c r="N69">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O69">
         <v>1.47</v>
@@ -18090,7 +18090,7 @@
         <v>4.7</v>
       </c>
       <c r="T69">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="U69">
         <v>1.87</v>
@@ -18102,7 +18102,7 @@
         <v>1.6</v>
       </c>
       <c r="X69">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y69">
         <v>10</v>
@@ -18114,7 +18114,7 @@
         <v>60</v>
       </c>
       <c r="AB69">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC69">
         <v>7.4</v>
@@ -18165,7 +18165,7 @@
         <v>17.5</v>
       </c>
       <c r="AS69">
-        <v>10.5</v>
+        <v>48</v>
       </c>
       <c r="AT69">
         <v>7.6</v>
@@ -18177,7 +18177,7 @@
         <v>12.5</v>
       </c>
       <c r="AW69">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX69">
         <v>14</v>
@@ -18195,7 +18195,7 @@
         <v>34</v>
       </c>
       <c r="BC69">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD69">
         <v>46</v>
@@ -18207,7 +18207,7 @@
         <v>25</v>
       </c>
       <c r="BG69">
-        <v>38</v>
+        <v>10.5</v>
       </c>
       <c r="BH69">
         <v>1000</v>
@@ -18296,7 +18296,7 @@
         <v>6.8</v>
       </c>
       <c r="H70">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="I70">
         <v>1.64</v>
@@ -18314,10 +18314,10 @@
         <v>1.05</v>
       </c>
       <c r="N70">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O70">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P70">
         <v>2.12</v>
@@ -18326,10 +18326,10 @@
         <v>1.73</v>
       </c>
       <c r="R70">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S70">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="T70">
         <v>1.81</v>
@@ -18395,7 +18395,7 @@
         <v>120</v>
       </c>
       <c r="AO70">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP70">
         <v>16</v>
@@ -18431,22 +18431,22 @@
         <v>18</v>
       </c>
       <c r="BA70">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BB70">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC70">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BD70">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BE70">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BF70">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="BG70">
         <v>6.2</v>
@@ -18532,7 +18532,7 @@
         <v>352</v>
       </c>
       <c r="F71">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="G71">
         <v>4.3</v>
@@ -18541,10 +18541,10 @@
         <v>2.08</v>
       </c>
       <c r="I71">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="J71">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K71">
         <v>4</v>
@@ -18556,7 +18556,7 @@
         <v>1.01</v>
       </c>
       <c r="N71">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O71">
         <v>1.24</v>
@@ -18574,13 +18574,13 @@
         <v>2.58</v>
       </c>
       <c r="T71">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U71">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V71">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="W71">
         <v>1.31</v>
@@ -18792,7 +18792,7 @@
         <v>3.9</v>
       </c>
       <c r="L72">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M72">
         <v>1.07</v>
@@ -18804,7 +18804,7 @@
         <v>1.32</v>
       </c>
       <c r="P72">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q72">
         <v>1.94</v>
@@ -18834,7 +18834,7 @@
         <v>18</v>
       </c>
       <c r="Z72">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA72">
         <v>110</v>
@@ -18843,10 +18843,10 @@
         <v>11.5</v>
       </c>
       <c r="AC72">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD72">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE72">
         <v>65</v>
@@ -18855,10 +18855,10 @@
         <v>16</v>
       </c>
       <c r="AG72">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH72">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AI72">
         <v>70</v>
@@ -18876,64 +18876,64 @@
         <v>130</v>
       </c>
       <c r="AN72">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO72">
         <v>70</v>
       </c>
       <c r="AP72">
+        <v>4.3</v>
+      </c>
+      <c r="AQ72">
+        <v>4.3</v>
+      </c>
+      <c r="AR72">
+        <v>4.8</v>
+      </c>
+      <c r="AS72">
+        <v>5.4</v>
+      </c>
+      <c r="AT72">
+        <v>3.8</v>
+      </c>
+      <c r="AU72">
         <v>3.4</v>
       </c>
-      <c r="AQ72">
-        <v>3.4</v>
-      </c>
-      <c r="AR72">
+      <c r="AV72">
+        <v>4.2</v>
+      </c>
+      <c r="AW72">
+        <v>5.2</v>
+      </c>
+      <c r="AX72">
+        <v>4.2</v>
+      </c>
+      <c r="AY72">
         <v>3.75</v>
       </c>
-      <c r="AS72">
-        <v>4</v>
-      </c>
-      <c r="AT72">
-        <v>3.1</v>
-      </c>
-      <c r="AU72">
-        <v>2.96</v>
-      </c>
-      <c r="AV72">
-        <v>3.5</v>
-      </c>
-      <c r="AW72">
-        <v>3.95</v>
-      </c>
-      <c r="AX72">
-        <v>3.35</v>
-      </c>
-      <c r="AY72">
-        <v>3.15</v>
-      </c>
       <c r="AZ72">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="BA72">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BB72">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC72">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="BD72">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="BE72">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BF72">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="BG72">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BH72">
         <v>1000</v>
@@ -19291,13 +19291,13 @@
         <v>2.88</v>
       </c>
       <c r="Q74">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T74">
         <v>1.43</v>
@@ -19530,7 +19530,7 @@
         <v>1.49</v>
       </c>
       <c r="P75">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q75">
         <v>2.46</v>
@@ -19984,7 +19984,7 @@
         <v>358</v>
       </c>
       <c r="F77">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G77">
         <v>1.72</v>
@@ -20017,7 +20017,7 @@
         <v>2.72</v>
       </c>
       <c r="Q77">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R77">
         <v>1.7</v>
@@ -20226,7 +20226,7 @@
         <v>359</v>
       </c>
       <c r="F78">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="G78">
         <v>990</v>
@@ -20250,13 +20250,13 @@
         <v>1.01</v>
       </c>
       <c r="N78">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O78">
         <v>1.02</v>
       </c>
       <c r="P78">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q78">
         <v>1.41</v>
@@ -20265,7 +20265,7 @@
         <v>1.18</v>
       </c>
       <c r="S78">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="T78">
         <v>1.11</v>
@@ -20274,7 +20274,7 @@
         <v>1.11</v>
       </c>
       <c r="V78">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W78">
         <v>1.08</v>
@@ -20489,7 +20489,7 @@
         <v>1.01</v>
       </c>
       <c r="M79">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N79">
         <v>4.3</v>
@@ -20501,7 +20501,7 @@
         <v>2.14</v>
       </c>
       <c r="Q79">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R79">
         <v>1.44</v>
@@ -20522,7 +20522,7 @@
         <v>2.48</v>
       </c>
       <c r="X79">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y79">
         <v>28</v>
@@ -20540,7 +20540,7 @@
         <v>12</v>
       </c>
       <c r="AD79">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE79">
         <v>1000</v>
@@ -20576,19 +20576,19 @@
         <v>1000</v>
       </c>
       <c r="AP79">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="AQ79">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR79">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="AS79">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="AT79">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU79">
         <v>8.199999999999999</v>
@@ -20597,7 +20597,7 @@
         <v>15</v>
       </c>
       <c r="AW79">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="AX79">
         <v>7</v>
@@ -20606,10 +20606,10 @@
         <v>7.8</v>
       </c>
       <c r="AZ79">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="BA79">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="BB79">
         <v>9.6</v>
@@ -20621,13 +20621,13 @@
         <v>20</v>
       </c>
       <c r="BE79">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="BF79">
         <v>5.5</v>
       </c>
       <c r="BG79">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="BH79">
         <v>1000</v>
@@ -20648,7 +20648,7 @@
         <v>1.88</v>
       </c>
       <c r="BN79">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO79">
         <v>2.88</v>
@@ -20660,10 +20660,10 @@
         <v>1.67</v>
       </c>
       <c r="BR79">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BS79">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BT79">
         <v>14.5</v>
@@ -20675,7 +20675,7 @@
         <v>1000</v>
       </c>
       <c r="BW79">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BX79">
         <v>1000</v>
@@ -20710,10 +20710,10 @@
         <v>361</v>
       </c>
       <c r="F80">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="G80">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="H80">
         <v>5.1</v>
@@ -20734,34 +20734,34 @@
         <v>1.07</v>
       </c>
       <c r="N80">
-        <v>2.86</v>
+        <v>3.65</v>
       </c>
       <c r="O80">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P80">
         <v>1.9</v>
       </c>
       <c r="Q80">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R80">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="S80">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="T80">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="U80">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="V80">
         <v>1.2</v>
       </c>
       <c r="W80">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="X80">
         <v>1000</v>
@@ -20830,13 +20830,13 @@
         <v>2.62</v>
       </c>
       <c r="AT80">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AU80">
         <v>2.16</v>
       </c>
       <c r="AV80">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW80">
         <v>2.62</v>
@@ -20845,10 +20845,10 @@
         <v>7.2</v>
       </c>
       <c r="AY80">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AZ80">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA80">
         <v>2.62</v>
@@ -20866,7 +20866,7 @@
         <v>2.62</v>
       </c>
       <c r="BF80">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG80">
         <v>2.62</v>
@@ -20988,7 +20988,7 @@
         <v>1.76</v>
       </c>
       <c r="R81">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S81">
         <v>2.92</v>
@@ -21042,7 +21042,7 @@
         <v>34</v>
       </c>
       <c r="AJ81">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AK81">
         <v>75</v>
@@ -21051,7 +21051,7 @@
         <v>75</v>
       </c>
       <c r="AM81">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN81">
         <v>85</v>
@@ -21066,7 +21066,7 @@
         <v>8</v>
       </c>
       <c r="AR81">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS81">
         <v>14.5</v>
@@ -21093,16 +21093,16 @@
         <v>16.5</v>
       </c>
       <c r="BA81">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB81">
         <v>8.800000000000001</v>
       </c>
       <c r="BC81">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BD81">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE81">
         <v>8.6</v>
@@ -21218,10 +21218,10 @@
         <v>1.05</v>
       </c>
       <c r="N82">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O82">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P82">
         <v>2.1</v>
@@ -21230,16 +21230,16 @@
         <v>1.78</v>
       </c>
       <c r="R82">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="S82">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="T82">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="U82">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="V82">
         <v>1.98</v>
@@ -21248,112 +21248,112 @@
         <v>1.29</v>
       </c>
       <c r="X82">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y82">
+        <v>10.5</v>
+      </c>
+      <c r="Z82">
+        <v>13.5</v>
+      </c>
+      <c r="AA82">
+        <v>24</v>
+      </c>
+      <c r="AB82">
+        <v>970</v>
+      </c>
+      <c r="AC82">
+        <v>9</v>
+      </c>
+      <c r="AD82">
+        <v>10.5</v>
+      </c>
+      <c r="AE82">
+        <v>20</v>
+      </c>
+      <c r="AF82">
+        <v>32</v>
+      </c>
+      <c r="AG82">
+        <v>970</v>
+      </c>
+      <c r="AH82">
+        <v>970</v>
+      </c>
+      <c r="AI82">
+        <v>32</v>
+      </c>
+      <c r="AJ82">
+        <v>80</v>
+      </c>
+      <c r="AK82">
+        <v>48</v>
+      </c>
+      <c r="AL82">
+        <v>55</v>
+      </c>
+      <c r="AM82">
+        <v>85</v>
+      </c>
+      <c r="AN82">
+        <v>44</v>
+      </c>
+      <c r="AO82">
+        <v>12.5</v>
+      </c>
+      <c r="AP82">
+        <v>13</v>
+      </c>
+      <c r="AQ82">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR82">
+        <v>11.5</v>
+      </c>
+      <c r="AS82">
+        <v>7.8</v>
+      </c>
+      <c r="AT82">
+        <v>7</v>
+      </c>
+      <c r="AU82">
+        <v>8</v>
+      </c>
+      <c r="AV82">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW82">
+        <v>7.4</v>
+      </c>
+      <c r="AX82">
+        <v>8.6</v>
+      </c>
+      <c r="AY82">
+        <v>14.5</v>
+      </c>
+      <c r="AZ82">
         <v>15</v>
       </c>
-      <c r="Z82">
-        <v>18.5</v>
-      </c>
-      <c r="AA82">
-        <v>32</v>
-      </c>
-      <c r="AB82">
-        <v>20</v>
-      </c>
-      <c r="AC82">
+      <c r="BA82">
+        <v>8.6</v>
+      </c>
+      <c r="BB82">
+        <v>10</v>
+      </c>
+      <c r="BC82">
+        <v>9.4</v>
+      </c>
+      <c r="BD82">
+        <v>36</v>
+      </c>
+      <c r="BE82">
+        <v>10</v>
+      </c>
+      <c r="BF82">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG82">
         <v>10.5</v>
-      </c>
-      <c r="AD82">
-        <v>12</v>
-      </c>
-      <c r="AE82">
-        <v>1000</v>
-      </c>
-      <c r="AF82">
-        <v>38</v>
-      </c>
-      <c r="AG82">
-        <v>20</v>
-      </c>
-      <c r="AH82">
-        <v>21</v>
-      </c>
-      <c r="AI82">
-        <v>36</v>
-      </c>
-      <c r="AJ82">
-        <v>1000</v>
-      </c>
-      <c r="AK82">
-        <v>1000</v>
-      </c>
-      <c r="AL82">
-        <v>1000</v>
-      </c>
-      <c r="AM82">
-        <v>100</v>
-      </c>
-      <c r="AN82">
-        <v>1000</v>
-      </c>
-      <c r="AO82">
-        <v>16.5</v>
-      </c>
-      <c r="AP82">
-        <v>2.5</v>
-      </c>
-      <c r="AQ82">
-        <v>6.8</v>
-      </c>
-      <c r="AR82">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS82">
-        <v>14</v>
-      </c>
-      <c r="AT82">
-        <v>11</v>
-      </c>
-      <c r="AU82">
-        <v>2.02</v>
-      </c>
-      <c r="AV82">
-        <v>6.8</v>
-      </c>
-      <c r="AW82">
-        <v>2.5</v>
-      </c>
-      <c r="AX82">
-        <v>21</v>
-      </c>
-      <c r="AY82">
-        <v>11</v>
-      </c>
-      <c r="AZ82">
-        <v>2.24</v>
-      </c>
-      <c r="BA82">
-        <v>20</v>
-      </c>
-      <c r="BB82">
-        <v>2.5</v>
-      </c>
-      <c r="BC82">
-        <v>2.5</v>
-      </c>
-      <c r="BD82">
-        <v>2.5</v>
-      </c>
-      <c r="BE82">
-        <v>2.44</v>
-      </c>
-      <c r="BF82">
-        <v>2.5</v>
-      </c>
-      <c r="BG82">
-        <v>8</v>
       </c>
       <c r="BH82">
         <v>1000</v>
@@ -21478,10 +21478,10 @@
         <v>2.62</v>
       </c>
       <c r="T83">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="U83">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V83">
         <v>1.21</v>
@@ -21526,10 +21526,10 @@
         <v>1000</v>
       </c>
       <c r="AJ83">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK83">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL83">
         <v>40</v>
@@ -21538,64 +21538,64 @@
         <v>1000</v>
       </c>
       <c r="AN83">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AO83">
         <v>1000</v>
       </c>
       <c r="AP83">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ83">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AR83">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AS83">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AT83">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AU83">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AV83">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AW83">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="AX83">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AY83">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AZ83">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="BA83">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="BB83">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="BC83">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="BD83">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BE83">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="BF83">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BG83">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="BH83">
         <v>5.5</v>
@@ -21619,7 +21619,7 @@
         <v>6.2</v>
       </c>
       <c r="BO83">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BP83">
         <v>15.5</v>
@@ -21684,7 +21684,7 @@
         <v>4.1</v>
       </c>
       <c r="H84">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="I84">
         <v>2.14</v>
@@ -21711,7 +21711,7 @@
         <v>2.28</v>
       </c>
       <c r="Q84">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="R84">
         <v>1.53</v>
@@ -21956,7 +21956,7 @@
         <v>2.28</v>
       </c>
       <c r="R85">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S85">
         <v>4.2</v>
@@ -22449,7 +22449,7 @@
         <v>1.52</v>
       </c>
       <c r="U87">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="V87">
         <v>1.35</v>
@@ -22888,7 +22888,7 @@
         <v>370</v>
       </c>
       <c r="F89">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G89">
         <v>2.2</v>
@@ -22912,7 +22912,7 @@
         <v>1.02</v>
       </c>
       <c r="N89">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O89">
         <v>1.14</v>
@@ -22942,7 +22942,7 @@
         <v>1.84</v>
       </c>
       <c r="X89">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y89">
         <v>28</v>
@@ -22954,7 +22954,7 @@
         <v>70</v>
       </c>
       <c r="AB89">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AC89">
         <v>13.5</v>
@@ -23130,7 +23130,7 @@
         <v>371</v>
       </c>
       <c r="F90">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="G90">
         <v>2.76</v>
@@ -23139,7 +23139,7 @@
         <v>2.88</v>
       </c>
       <c r="I90">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="J90">
         <v>3.05</v>
@@ -23178,7 +23178,7 @@
         <v>1.11</v>
       </c>
       <c r="V90">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W90">
         <v>1.56</v>
@@ -23396,7 +23396,7 @@
         <v>1.01</v>
       </c>
       <c r="N91">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O91">
         <v>1.15</v>
@@ -23411,7 +23411,7 @@
         <v>1.59</v>
       </c>
       <c r="S91">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="T91">
         <v>1.56</v>
@@ -23453,7 +23453,7 @@
         <v>13</v>
       </c>
       <c r="AG91">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH91">
         <v>24</v>
@@ -23462,7 +23462,7 @@
         <v>1000</v>
       </c>
       <c r="AJ91">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AK91">
         <v>17.5</v>
@@ -23483,7 +23483,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ91">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AR91">
         <v>1.03</v>
@@ -23492,22 +23492,22 @@
         <v>1.03</v>
       </c>
       <c r="AT91">
+        <v>8</v>
+      </c>
+      <c r="AU91">
         <v>8.199999999999999</v>
       </c>
-      <c r="AU91">
-        <v>8.4</v>
-      </c>
       <c r="AV91">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW91">
         <v>1.03</v>
       </c>
       <c r="AX91">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AY91">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AZ91">
         <v>13</v>
@@ -23516,13 +23516,13 @@
         <v>1.03</v>
       </c>
       <c r="BB91">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC91">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD91">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BE91">
         <v>1.03</v>
@@ -23537,7 +23537,7 @@
         <v>6.2</v>
       </c>
       <c r="BI91">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BJ91">
         <v>13.5</v>
@@ -23558,10 +23558,10 @@
         <v>3.1</v>
       </c>
       <c r="BP91">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ91">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BR91">
         <v>28</v>
@@ -23570,10 +23570,10 @@
         <v>2.84</v>
       </c>
       <c r="BT91">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BU91">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BV91">
         <v>1000</v>
@@ -23588,7 +23588,7 @@
         <v>3</v>
       </c>
       <c r="BZ91">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA91">
         <v>2.64</v>
@@ -23635,10 +23635,10 @@
         <v>1.01</v>
       </c>
       <c r="M92">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N92">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O92">
         <v>1.4</v>
@@ -23650,7 +23650,7 @@
         <v>2.14</v>
       </c>
       <c r="R92">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S92">
         <v>3.85</v>
@@ -24382,10 +24382,10 @@
         <v>2.52</v>
       </c>
       <c r="T95">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="U95">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V95">
         <v>1.42</v>
@@ -24624,10 +24624,10 @@
         <v>2.74</v>
       </c>
       <c r="T96">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U96">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V96">
         <v>1.6</v>
@@ -24824,28 +24824,28 @@
         <v>378</v>
       </c>
       <c r="F97">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="G97">
         <v>1.28</v>
       </c>
       <c r="H97">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="I97">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J97">
         <v>6.2</v>
       </c>
       <c r="K97">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L97">
         <v>1.01</v>
       </c>
       <c r="M97">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N97">
         <v>4.2</v>
@@ -24860,16 +24860,16 @@
         <v>1.69</v>
       </c>
       <c r="R97">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S97">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T97">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="U97">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="V97">
         <v>1.04</v>
@@ -24884,13 +24884,13 @@
         <v>55</v>
       </c>
       <c r="Z97">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AA97">
         <v>1000</v>
       </c>
       <c r="AB97">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC97">
         <v>16.5</v>
@@ -24899,7 +24899,7 @@
         <v>950</v>
       </c>
       <c r="AE97">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="AF97">
         <v>7.4</v>
@@ -24911,7 +24911,7 @@
         <v>50</v>
       </c>
       <c r="AI97">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AJ97">
         <v>10.5</v>
@@ -24923,127 +24923,127 @@
         <v>60</v>
       </c>
       <c r="AM97">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AN97">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AO97">
         <v>1000</v>
       </c>
       <c r="AP97">
-        <v>4.9</v>
+        <v>16.5</v>
       </c>
       <c r="AQ97">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AR97">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AS97">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT97">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AU97">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="AV97">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW97">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AX97">
         <v>5.9</v>
       </c>
       <c r="AY97">
-        <v>4.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ97">
-        <v>5.4</v>
+        <v>34</v>
       </c>
       <c r="BA97">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BB97">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BC97">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="BD97">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE97">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF97">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BG97">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH97">
         <v>1000</v>
       </c>
       <c r="BI97">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BJ97">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BK97">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="BL97">
         <v>1000</v>
       </c>
       <c r="BM97">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BN97">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO97">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BP97">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ97">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BR97">
         <v>40</v>
       </c>
       <c r="BS97">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="BT97">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BU97">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="BV97">
         <v>1000</v>
       </c>
       <c r="BW97">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BX97">
         <v>1000</v>
       </c>
       <c r="BY97">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BZ97">
         <v>17</v>
       </c>
       <c r="CA97">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CB97" t="s">
         <v>408</v>
@@ -25093,7 +25093,7 @@
         <v>5.7</v>
       </c>
       <c r="O98">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P98">
         <v>2.58</v>
@@ -25120,112 +25120,112 @@
         <v>1.18</v>
       </c>
       <c r="X98">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y98">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z98">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA98">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AB98">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC98">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD98">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE98">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AF98">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG98">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AH98">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI98">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AJ98">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK98">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL98">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM98">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN98">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO98">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AP98">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AQ98">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR98">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS98">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AT98">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AU98">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV98">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW98">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AX98">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AY98">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AZ98">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA98">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB98">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BC98">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BD98">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE98">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BF98">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BG98">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH98">
         <v>1000</v>
@@ -25338,7 +25338,7 @@
         <v>1.22</v>
       </c>
       <c r="P99">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q99">
         <v>1.71</v>
@@ -25550,7 +25550,7 @@
         <v>381</v>
       </c>
       <c r="F100">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G100">
         <v>2.6</v>
@@ -25559,25 +25559,25 @@
         <v>2.96</v>
       </c>
       <c r="I100">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J100">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K100">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L100">
         <v>1.01</v>
       </c>
       <c r="M100">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N100">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O100">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P100">
         <v>1.9</v>
@@ -25586,130 +25586,130 @@
         <v>1.97</v>
       </c>
       <c r="R100">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S100">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="T100">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="U100">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="V100">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W100">
         <v>1.62</v>
       </c>
       <c r="X100">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y100">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="Z100">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AA100">
+        <v>70</v>
+      </c>
+      <c r="AB100">
+        <v>10.5</v>
+      </c>
+      <c r="AC100">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD100">
+        <v>14</v>
+      </c>
+      <c r="AE100">
+        <v>50</v>
+      </c>
+      <c r="AF100">
+        <v>17</v>
+      </c>
+      <c r="AG100">
+        <v>12</v>
+      </c>
+      <c r="AH100">
+        <v>25</v>
+      </c>
+      <c r="AI100">
         <v>65</v>
-      </c>
-      <c r="AB100">
-        <v>14.5</v>
-      </c>
-      <c r="AC100">
-        <v>10</v>
-      </c>
-      <c r="AD100">
-        <v>18</v>
-      </c>
-      <c r="AE100">
-        <v>46</v>
-      </c>
-      <c r="AF100">
-        <v>23</v>
-      </c>
-      <c r="AG100">
-        <v>16</v>
-      </c>
-      <c r="AH100">
-        <v>23</v>
-      </c>
-      <c r="AI100">
-        <v>60</v>
       </c>
       <c r="AJ100">
         <v>50</v>
       </c>
       <c r="AK100">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL100">
         <v>55</v>
       </c>
       <c r="AM100">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN100">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO100">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP100">
+        <v>12</v>
+      </c>
+      <c r="AQ100">
+        <v>10.5</v>
+      </c>
+      <c r="AR100">
+        <v>6.8</v>
+      </c>
+      <c r="AS100">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT100">
+        <v>9</v>
+      </c>
+      <c r="AU100">
+        <v>7</v>
+      </c>
+      <c r="AV100">
+        <v>12</v>
+      </c>
+      <c r="AW100">
+        <v>25</v>
+      </c>
+      <c r="AX100">
+        <v>6.2</v>
+      </c>
+      <c r="AY100">
         <v>10</v>
       </c>
-      <c r="AQ100">
+      <c r="AZ100">
+        <v>6.2</v>
+      </c>
+      <c r="BA100">
+        <v>32</v>
+      </c>
+      <c r="BB100">
+        <v>26</v>
+      </c>
+      <c r="BC100">
+        <v>19.5</v>
+      </c>
+      <c r="BD100">
+        <v>29</v>
+      </c>
+      <c r="BE100">
         <v>9</v>
       </c>
-      <c r="AR100">
-        <v>15</v>
-      </c>
-      <c r="AS100">
-        <v>2.68</v>
-      </c>
-      <c r="AT100">
-        <v>2.34</v>
-      </c>
-      <c r="AU100">
-        <v>6</v>
-      </c>
-      <c r="AV100">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW100">
-        <v>2.64</v>
-      </c>
-      <c r="AX100">
-        <v>11.5</v>
-      </c>
-      <c r="AY100">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ100">
-        <v>2.5</v>
-      </c>
-      <c r="BA100">
-        <v>2.68</v>
-      </c>
-      <c r="BB100">
-        <v>2.66</v>
-      </c>
-      <c r="BC100">
-        <v>20</v>
-      </c>
-      <c r="BD100">
-        <v>2.66</v>
-      </c>
-      <c r="BE100">
-        <v>2.8</v>
-      </c>
       <c r="BF100">
-        <v>2.8</v>
+        <v>17.5</v>
       </c>
       <c r="BG100">
-        <v>2.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH100">
         <v>1000</v>
@@ -25807,7 +25807,7 @@
         <v>3.4</v>
       </c>
       <c r="K101">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L101">
         <v>1.01</v>
@@ -25819,7 +25819,7 @@
         <v>1.1</v>
       </c>
       <c r="O101">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P101">
         <v>1.92</v>
@@ -25831,13 +25831,13 @@
         <v>1.32</v>
       </c>
       <c r="S101">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T101">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="U101">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V101">
         <v>1.35</v>
@@ -25858,13 +25858,13 @@
         <v>1000</v>
       </c>
       <c r="AB101">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC101">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD101">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE101">
         <v>1000</v>
@@ -25876,19 +25876,19 @@
         <v>1000</v>
       </c>
       <c r="AH101">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI101">
         <v>1000</v>
       </c>
       <c r="AJ101">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK101">
         <v>1000</v>
       </c>
       <c r="AL101">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM101">
         <v>1000</v>
@@ -25900,76 +25900,76 @@
         <v>1000</v>
       </c>
       <c r="AP101">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="AQ101">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="AR101">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="AS101">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="AT101">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="AU101">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AV101">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="AW101">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="AX101">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="AY101">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="AZ101">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="BA101">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="BB101">
-        <v>1.13</v>
+        <v>1.48</v>
       </c>
       <c r="BC101">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="BD101">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="BE101">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="BF101">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="BG101">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="BH101">
         <v>1000</v>
       </c>
       <c r="BI101">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BJ101">
         <v>13</v>
       </c>
       <c r="BK101">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BL101">
         <v>1000</v>
       </c>
       <c r="BM101">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BN101">
         <v>6.8</v>
@@ -25978,7 +25978,7 @@
         <v>3.55</v>
       </c>
       <c r="BP101">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ101">
         <v>1.76</v>
@@ -25987,7 +25987,7 @@
         <v>40</v>
       </c>
       <c r="BS101">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BT101">
         <v>9.199999999999999</v>
@@ -25996,19 +25996,19 @@
         <v>4.5</v>
       </c>
       <c r="BV101">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BW101">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BX101">
         <v>50</v>
       </c>
       <c r="BY101">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BZ101">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA101">
         <v>1.81</v>
@@ -26040,34 +26040,34 @@
         <v>3.35</v>
       </c>
       <c r="H102">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I102">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="J102">
         <v>3.75</v>
       </c>
       <c r="K102">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L102">
         <v>1.01</v>
       </c>
       <c r="M102">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N102">
         <v>4.3</v>
       </c>
       <c r="O102">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P102">
         <v>2.1</v>
       </c>
       <c r="Q102">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="R102">
         <v>1.45</v>
@@ -26088,7 +26088,7 @@
         <v>1.42</v>
       </c>
       <c r="X102">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y102">
         <v>12.5</v>
@@ -26291,7 +26291,7 @@
         <v>5.9</v>
       </c>
       <c r="K103">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L103">
         <v>1.22</v>
@@ -26303,7 +26303,7 @@
         <v>2.6</v>
       </c>
       <c r="O103">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P103">
         <v>2.6</v>
@@ -26333,7 +26333,7 @@
         <v>1000</v>
       </c>
       <c r="Y103">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z103">
         <v>1000</v>
@@ -26342,19 +26342,19 @@
         <v>1000</v>
       </c>
       <c r="AB103">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC103">
         <v>1000</v>
       </c>
       <c r="AD103">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE103">
         <v>1000</v>
       </c>
       <c r="AF103">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG103">
         <v>1000</v>
@@ -26372,70 +26372,70 @@
         <v>1000</v>
       </c>
       <c r="AL103">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM103">
         <v>1000</v>
       </c>
       <c r="AN103">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="AO103">
         <v>1000</v>
       </c>
       <c r="AP103">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="AQ103">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="AR103">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="AS103">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="AT103">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="AU103">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="AV103">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="AW103">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="AX103">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="AY103">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="AZ103">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BA103">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BB103">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BC103">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BD103">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BE103">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BF103">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG103">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BH103">
         <v>1000</v>
@@ -26521,13 +26521,13 @@
         <v>2.56</v>
       </c>
       <c r="G104">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="H104">
         <v>2.56</v>
       </c>
       <c r="I104">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="J104">
         <v>3.45</v>
@@ -26566,10 +26566,10 @@
         <v>2.06</v>
       </c>
       <c r="V104">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W104">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="X104">
         <v>1000</v>
@@ -26784,10 +26784,10 @@
         <v>1.07</v>
       </c>
       <c r="N105">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O105">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P105">
         <v>1.86</v>
@@ -26799,7 +26799,7 @@
         <v>1.31</v>
       </c>
       <c r="S105">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T105">
         <v>1.87</v>
@@ -26832,28 +26832,28 @@
         <v>8.4</v>
       </c>
       <c r="AD105">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE105">
         <v>65</v>
       </c>
       <c r="AF105">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG105">
         <v>12.5</v>
       </c>
       <c r="AH105">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI105">
         <v>85</v>
       </c>
       <c r="AJ105">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK105">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL105">
         <v>40</v>
@@ -26862,7 +26862,7 @@
         <v>140</v>
       </c>
       <c r="AN105">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO105">
         <v>85</v>
@@ -26871,28 +26871,28 @@
         <v>10</v>
       </c>
       <c r="AQ105">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AR105">
         <v>20</v>
       </c>
       <c r="AS105">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT105">
         <v>6.4</v>
       </c>
       <c r="AU105">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AV105">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AW105">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AX105">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AY105">
         <v>7.8</v>
@@ -26901,25 +26901,25 @@
         <v>14.5</v>
       </c>
       <c r="BA105">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB105">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BC105">
         <v>15</v>
       </c>
       <c r="BD105">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BE105">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF105">
         <v>11</v>
       </c>
       <c r="BG105">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BH105">
         <v>4</v>
@@ -26943,7 +26943,7 @@
         <v>6.2</v>
       </c>
       <c r="BO105">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BP105">
         <v>19</v>
@@ -27020,7 +27020,7 @@
         <v>4.1</v>
       </c>
       <c r="L106">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M106">
         <v>1.05</v>
@@ -27104,64 +27104,64 @@
         <v>1000</v>
       </c>
       <c r="AN106">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO106">
         <v>1000</v>
       </c>
       <c r="AP106">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AQ106">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AR106">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AS106">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AT106">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AU106">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AV106">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AW106">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AX106">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AY106">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AZ106">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BA106">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BB106">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BC106">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BD106">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BE106">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BF106">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BG106">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BH106">
         <v>1000</v>
@@ -27286,10 +27286,10 @@
         <v>4.2</v>
       </c>
       <c r="T107">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U107">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V107">
         <v>2.12</v>
@@ -27486,22 +27486,22 @@
         <v>389</v>
       </c>
       <c r="F108">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="G108">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="H108">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="I108">
-        <v>990</v>
+        <v>7.6</v>
       </c>
       <c r="J108">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="K108">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="L108">
         <v>1.01</v>
@@ -27510,142 +27510,142 @@
         <v>1.03</v>
       </c>
       <c r="N108">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O108">
         <v>1.17</v>
       </c>
       <c r="P108">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="Q108">
         <v>1.52</v>
       </c>
       <c r="R108">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="S108">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T108">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U108">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="V108">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W108">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="X108">
         <v>29</v>
       </c>
       <c r="Y108">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="Z108">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA108">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AB108">
+        <v>12.5</v>
+      </c>
+      <c r="AC108">
+        <v>12.5</v>
+      </c>
+      <c r="AD108">
+        <v>34</v>
+      </c>
+      <c r="AE108">
+        <v>85</v>
+      </c>
+      <c r="AF108">
         <v>12</v>
-      </c>
-      <c r="AC108">
-        <v>13</v>
-      </c>
-      <c r="AD108">
-        <v>40</v>
-      </c>
-      <c r="AE108">
-        <v>110</v>
-      </c>
-      <c r="AF108">
-        <v>11.5</v>
       </c>
       <c r="AG108">
         <v>11</v>
       </c>
       <c r="AH108">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI108">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ108">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK108">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AL108">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM108">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN108">
+        <v>5.9</v>
+      </c>
+      <c r="AO108">
+        <v>85</v>
+      </c>
+      <c r="AP108">
+        <v>6.8</v>
+      </c>
+      <c r="AQ108">
+        <v>6.8</v>
+      </c>
+      <c r="AR108">
+        <v>7.8</v>
+      </c>
+      <c r="AS108">
+        <v>8.4</v>
+      </c>
+      <c r="AT108">
+        <v>5.2</v>
+      </c>
+      <c r="AU108">
+        <v>5.2</v>
+      </c>
+      <c r="AV108">
+        <v>6.6</v>
+      </c>
+      <c r="AW108">
+        <v>8</v>
+      </c>
+      <c r="AX108">
+        <v>5.1</v>
+      </c>
+      <c r="AY108">
+        <v>4.9</v>
+      </c>
+      <c r="AZ108">
+        <v>6.2</v>
+      </c>
+      <c r="BA108">
+        <v>7.8</v>
+      </c>
+      <c r="BB108">
+        <v>5.5</v>
+      </c>
+      <c r="BC108">
         <v>5.6</v>
       </c>
-      <c r="AO108">
-        <v>1000</v>
-      </c>
-      <c r="AP108">
-        <v>6</v>
-      </c>
-      <c r="AQ108">
-        <v>6.2</v>
-      </c>
-      <c r="AR108">
+      <c r="BD108">
         <v>6.8</v>
       </c>
-      <c r="AS108">
-        <v>7.2</v>
-      </c>
-      <c r="AT108">
-        <v>4.6</v>
-      </c>
-      <c r="AU108">
-        <v>4.8</v>
-      </c>
-      <c r="AV108">
-        <v>6</v>
-      </c>
-      <c r="AW108">
-        <v>7</v>
-      </c>
-      <c r="AX108">
-        <v>4.5</v>
-      </c>
-      <c r="AY108">
-        <v>4.5</v>
-      </c>
-      <c r="AZ108">
-        <v>5.7</v>
-      </c>
-      <c r="BA108">
-        <v>6.8</v>
-      </c>
-      <c r="BB108">
-        <v>4.9</v>
-      </c>
-      <c r="BC108">
-        <v>5</v>
-      </c>
-      <c r="BD108">
-        <v>6</v>
-      </c>
       <c r="BE108">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF108">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BG108">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH108">
         <v>1000</v>
@@ -27973,163 +27973,163 @@
         <v>3.2</v>
       </c>
       <c r="G110">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="H110">
+        <v>2.2</v>
+      </c>
+      <c r="I110">
+        <v>2.44</v>
+      </c>
+      <c r="J110">
+        <v>3.4</v>
+      </c>
+      <c r="K110">
+        <v>3.85</v>
+      </c>
+      <c r="L110">
+        <v>1.01</v>
+      </c>
+      <c r="M110">
+        <v>1.07</v>
+      </c>
+      <c r="N110">
+        <v>3.7</v>
+      </c>
+      <c r="O110">
+        <v>1.3</v>
+      </c>
+      <c r="P110">
+        <v>1.93</v>
+      </c>
+      <c r="Q110">
+        <v>1.91</v>
+      </c>
+      <c r="R110">
+        <v>1.35</v>
+      </c>
+      <c r="S110">
+        <v>3.25</v>
+      </c>
+      <c r="T110">
+        <v>1.73</v>
+      </c>
+      <c r="U110">
         <v>2.14</v>
       </c>
-      <c r="I110">
-        <v>2.64</v>
-      </c>
-      <c r="J110">
-        <v>2.58</v>
-      </c>
-      <c r="K110">
-        <v>4.7</v>
-      </c>
-      <c r="L110">
-        <v>1.01</v>
-      </c>
-      <c r="M110">
-        <v>1.06</v>
-      </c>
-      <c r="N110">
-        <v>3.4</v>
-      </c>
-      <c r="O110">
-        <v>1.28</v>
-      </c>
-      <c r="P110">
-        <v>1.89</v>
-      </c>
-      <c r="Q110">
-        <v>1.89</v>
-      </c>
-      <c r="R110">
-        <v>1.34</v>
-      </c>
-      <c r="S110">
-        <v>3</v>
-      </c>
-      <c r="T110">
-        <v>1.12</v>
-      </c>
-      <c r="U110">
-        <v>1.98</v>
-      </c>
       <c r="V110">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W110">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="X110">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y110">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z110">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA110">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB110">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC110">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD110">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE110">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF110">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG110">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH110">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI110">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ110">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK110">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL110">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM110">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN110">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO110">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP110">
-        <v>1.11</v>
+        <v>12.5</v>
       </c>
       <c r="AQ110">
-        <v>1.11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR110">
-        <v>1.11</v>
+        <v>12.5</v>
       </c>
       <c r="AS110">
-        <v>1.11</v>
+        <v>5.4</v>
       </c>
       <c r="AT110">
-        <v>1.11</v>
+        <v>11.5</v>
       </c>
       <c r="AU110">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV110">
-        <v>1.11</v>
+        <v>9.6</v>
       </c>
       <c r="AW110">
-        <v>1.11</v>
+        <v>20</v>
       </c>
       <c r="AX110">
-        <v>1.11</v>
+        <v>20</v>
       </c>
       <c r="AY110">
-        <v>1.11</v>
+        <v>12</v>
       </c>
       <c r="AZ110">
-        <v>1.11</v>
+        <v>14.5</v>
       </c>
       <c r="BA110">
-        <v>1.11</v>
+        <v>5.6</v>
       </c>
       <c r="BB110">
-        <v>1.11</v>
+        <v>5.9</v>
       </c>
       <c r="BC110">
-        <v>1.11</v>
+        <v>5.6</v>
       </c>
       <c r="BD110">
-        <v>1.11</v>
+        <v>5.8</v>
       </c>
       <c r="BE110">
-        <v>1.11</v>
+        <v>6</v>
       </c>
       <c r="BF110">
-        <v>1.11</v>
+        <v>5.6</v>
       </c>
       <c r="BG110">
-        <v>1.11</v>
+        <v>14</v>
       </c>
       <c r="BH110">
         <v>1000</v>
@@ -28218,10 +28218,10 @@
         <v>1.95</v>
       </c>
       <c r="H111">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I111">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J111">
         <v>3.7</v>
@@ -28260,7 +28260,7 @@
         <v>1.97</v>
       </c>
       <c r="V111">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W111">
         <v>2.04</v>
@@ -28287,7 +28287,7 @@
         <v>20</v>
       </c>
       <c r="AE111">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AF111">
         <v>13</v>
@@ -28329,10 +28329,10 @@
         <v>22</v>
       </c>
       <c r="AS111">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT111">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AU111">
         <v>3.7</v>
@@ -28344,16 +28344,16 @@
         <v>5.5</v>
       </c>
       <c r="AX111">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AY111">
         <v>7.6</v>
       </c>
       <c r="AZ111">
-        <v>4.8</v>
+        <v>17.5</v>
       </c>
       <c r="BA111">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB111">
         <v>4.8</v>
@@ -28365,7 +28365,7 @@
         <v>5.2</v>
       </c>
       <c r="BE111">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF111">
         <v>4.3</v>
@@ -28460,16 +28460,16 @@
         <v>2.5</v>
       </c>
       <c r="H112">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="I112">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="J112">
         <v>3.6</v>
       </c>
       <c r="K112">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L112">
         <v>1.01</v>
@@ -28478,16 +28478,16 @@
         <v>1.01</v>
       </c>
       <c r="N112">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="O112">
         <v>1.17</v>
       </c>
       <c r="P112">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="Q112">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R112">
         <v>1.61</v>
@@ -28499,10 +28499,10 @@
         <v>1.48</v>
       </c>
       <c r="U112">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V112">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W112">
         <v>1.66</v>
@@ -28616,64 +28616,64 @@
         <v>1.01</v>
       </c>
       <c r="BH112">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BI112">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ112">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK112">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL112">
         <v>1000</v>
       </c>
       <c r="BM112">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BN112">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO112">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP112">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ112">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="BR112">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS112">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BT112">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU112">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV112">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW112">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BX112">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY112">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BZ112">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA112">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="CB112" t="s">
         <v>408</v>
@@ -28699,7 +28699,7 @@
         <v>2.74</v>
       </c>
       <c r="G113">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H113">
         <v>2.44</v>
@@ -28720,28 +28720,28 @@
         <v>1.02</v>
       </c>
       <c r="N113">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O113">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="P113">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="Q113">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R113">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S113">
         <v>2.04</v>
       </c>
       <c r="T113">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="U113">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="V113">
         <v>1.65</v>
@@ -28756,25 +28756,25 @@
         <v>21</v>
       </c>
       <c r="Z113">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA113">
         <v>38</v>
       </c>
       <c r="AB113">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC113">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD113">
         <v>13</v>
       </c>
       <c r="AE113">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF113">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG113">
         <v>14.5</v>
@@ -28783,7 +28783,7 @@
         <v>14.5</v>
       </c>
       <c r="AI113">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ113">
         <v>44</v>
@@ -28795,7 +28795,7 @@
         <v>28</v>
       </c>
       <c r="AM113">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AN113">
         <v>13</v>
@@ -28807,25 +28807,25 @@
         <v>23</v>
       </c>
       <c r="AQ113">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR113">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS113">
         <v>30</v>
       </c>
       <c r="AT113">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AU113">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV113">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW113">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX113">
         <v>22</v>
@@ -28843,19 +28843,19 @@
         <v>36</v>
       </c>
       <c r="BC113">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD113">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE113">
         <v>36</v>
       </c>
       <c r="BF113">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG113">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH113">
         <v>1000</v>
@@ -28980,10 +28980,10 @@
         <v>3.15</v>
       </c>
       <c r="T114">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U114">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V114">
         <v>1.44</v>
@@ -29183,7 +29183,7 @@
         <v>1.68</v>
       </c>
       <c r="G115">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H115">
         <v>4.5</v>
@@ -29431,7 +29431,7 @@
         <v>2.62</v>
       </c>
       <c r="I116">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="J116">
         <v>3</v>
@@ -29446,7 +29446,7 @@
         <v>1.12</v>
       </c>
       <c r="N116">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O116">
         <v>1.53</v>
@@ -29455,13 +29455,13 @@
         <v>1.56</v>
       </c>
       <c r="Q116">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R116">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S116">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="T116">
         <v>2.04</v>
@@ -29521,7 +29521,7 @@
         <v>100</v>
       </c>
       <c r="AM116">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN116">
         <v>85</v>
@@ -29551,7 +29551,7 @@
         <v>11</v>
       </c>
       <c r="AW116">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX116">
         <v>17.5</v>
@@ -29563,22 +29563,22 @@
         <v>18.5</v>
       </c>
       <c r="BA116">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB116">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC116">
         <v>40</v>
       </c>
       <c r="BD116">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE116">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF116">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG116">
         <v>30</v>
@@ -29664,22 +29664,22 @@
         <v>398</v>
       </c>
       <c r="F117">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="G117">
         <v>3.15</v>
       </c>
       <c r="H117">
+        <v>2.88</v>
+      </c>
+      <c r="I117">
+        <v>3.15</v>
+      </c>
+      <c r="J117">
         <v>2.9</v>
       </c>
-      <c r="I117">
-        <v>3.2</v>
-      </c>
-      <c r="J117">
-        <v>2.84</v>
-      </c>
       <c r="K117">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="L117">
         <v>1.01</v>
@@ -29688,70 +29688,70 @@
         <v>1.16</v>
       </c>
       <c r="N117">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="O117">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="P117">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="Q117">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R117">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S117">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="T117">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="U117">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="V117">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W117">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X117">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="Y117">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="Z117">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AA117">
         <v>80</v>
       </c>
       <c r="AB117">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AC117">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AD117">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AE117">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AF117">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AG117">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AH117">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI117">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ117">
         <v>90</v>
@@ -29760,70 +29760,70 @@
         <v>60</v>
       </c>
       <c r="AL117">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM117">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN117">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO117">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP117">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ117">
-        <v>2.66</v>
+        <v>6.8</v>
       </c>
       <c r="AR117">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="AS117">
-        <v>3.6</v>
+        <v>9</v>
       </c>
       <c r="AT117">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AU117">
-        <v>2.56</v>
+        <v>6.2</v>
       </c>
       <c r="AV117">
-        <v>3.1</v>
+        <v>13</v>
       </c>
       <c r="AW117">
-        <v>3.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX117">
         <v>11</v>
       </c>
       <c r="AY117">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AZ117">
-        <v>3.35</v>
+        <v>7.6</v>
       </c>
       <c r="BA117">
-        <v>3.75</v>
+        <v>9.6</v>
       </c>
       <c r="BB117">
-        <v>3.6</v>
+        <v>9</v>
       </c>
       <c r="BC117">
         <v>32</v>
       </c>
       <c r="BD117">
-        <v>3.75</v>
+        <v>9.6</v>
       </c>
       <c r="BE117">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="BF117">
-        <v>3.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG117">
-        <v>3.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH117">
         <v>1000</v>
@@ -29835,13 +29835,13 @@
         <v>18</v>
       </c>
       <c r="BK117">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="BL117">
         <v>1000</v>
       </c>
       <c r="BM117">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BN117">
         <v>7.8</v>
@@ -29853,16 +29853,16 @@
         <v>44</v>
       </c>
       <c r="BQ117">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BR117">
         <v>1000</v>
       </c>
       <c r="BS117">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BT117">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU117">
         <v>3.95</v>
@@ -29871,19 +29871,19 @@
         <v>50</v>
       </c>
       <c r="BW117">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BX117">
         <v>1000</v>
       </c>
       <c r="BY117">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BZ117">
         <v>1000</v>
       </c>
       <c r="CA117">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CB117" t="s">
         <v>408</v>
@@ -30181,19 +30181,19 @@
         <v>1.55</v>
       </c>
       <c r="Q119">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R119">
         <v>1.14</v>
       </c>
       <c r="S119">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T119">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U119">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V119">
         <v>1.56</v>
@@ -30399,7 +30399,7 @@
         <v>3.85</v>
       </c>
       <c r="I120">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J120">
         <v>3.3</v>
@@ -30432,10 +30432,10 @@
         <v>2.26</v>
       </c>
       <c r="T120">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U120">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V120">
         <v>1.04</v>
@@ -30641,7 +30641,7 @@
         <v>2.02</v>
       </c>
       <c r="I121">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="J121">
         <v>3.55</v>
@@ -30662,25 +30662,25 @@
         <v>1.28</v>
       </c>
       <c r="P121">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q121">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R121">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S121">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T121">
-        <v>1.69</v>
+        <v>1.11</v>
       </c>
       <c r="U121">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V121">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="W121">
         <v>1.3</v>
@@ -30889,7 +30889,7 @@
         <v>3.3</v>
       </c>
       <c r="K122">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L122">
         <v>1.01</v>
@@ -30907,7 +30907,7 @@
         <v>1.66</v>
       </c>
       <c r="Q122">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R122">
         <v>1.22</v>
@@ -31116,7 +31116,7 @@
         <v>404</v>
       </c>
       <c r="F123">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="G123">
         <v>2.82</v>
@@ -31134,7 +31134,7 @@
         <v>3.55</v>
       </c>
       <c r="L123">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M123">
         <v>1.09</v>
@@ -31155,7 +31155,7 @@
         <v>1.25</v>
       </c>
       <c r="S123">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T123">
         <v>1.86</v>
@@ -31164,7 +31164,7 @@
         <v>1.92</v>
       </c>
       <c r="V123">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W123">
         <v>1.55</v>
@@ -31191,7 +31191,7 @@
         <v>16</v>
       </c>
       <c r="AE123">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AF123">
         <v>19</v>
@@ -31218,7 +31218,7 @@
         <v>150</v>
       </c>
       <c r="AN123">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO123">
         <v>55</v>
@@ -31230,22 +31230,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR123">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS123">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT123">
         <v>7.2</v>
       </c>
       <c r="AU123">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AV123">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW123">
-        <v>4.7</v>
+        <v>30</v>
       </c>
       <c r="AX123">
         <v>12.5</v>
@@ -31254,28 +31254,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ123">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA123">
+        <v>5</v>
+      </c>
+      <c r="BB123">
         <v>4.8</v>
       </c>
-      <c r="BB123">
+      <c r="BC123">
         <v>4.7</v>
       </c>
-      <c r="BC123">
-        <v>4.6</v>
-      </c>
       <c r="BD123">
-        <v>4.8</v>
+        <v>38</v>
       </c>
       <c r="BE123">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF123">
         <v>4.6</v>
       </c>
       <c r="BG123">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH123">
         <v>3.1</v>
@@ -31358,7 +31358,7 @@
         <v>405</v>
       </c>
       <c r="F124">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G124">
         <v>3.3</v>
@@ -31367,13 +31367,13 @@
         <v>2.52</v>
       </c>
       <c r="I124">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="J124">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K124">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="L124">
         <v>1.01</v>
@@ -31385,13 +31385,13 @@
         <v>2.82</v>
       </c>
       <c r="O124">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P124">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q124">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R124">
         <v>1.22</v>
@@ -31400,10 +31400,10 @@
         <v>4</v>
       </c>
       <c r="T124">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="U124">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="V124">
         <v>1.59</v>
@@ -31642,7 +31642,7 @@
         <v>4.1</v>
       </c>
       <c r="T125">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U125">
         <v>1.6</v>
@@ -31845,7 +31845,7 @@
         <v>2.14</v>
       </c>
       <c r="G126">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H126">
         <v>4.1</v>
@@ -31860,7 +31860,7 @@
         <v>3.35</v>
       </c>
       <c r="L126">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="M126">
         <v>1.12</v>
@@ -31887,13 +31887,13 @@
         <v>2.04</v>
       </c>
       <c r="U126">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V126">
         <v>1.28</v>
       </c>
       <c r="W126">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="X126">
         <v>9.6</v>
@@ -31953,7 +31953,7 @@
         <v>7</v>
       </c>
       <c r="AQ126">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="AR126">
         <v>5.1</v>
@@ -31965,22 +31965,22 @@
         <v>3.35</v>
       </c>
       <c r="AU126">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="AV126">
-        <v>15.5</v>
+        <v>4.7</v>
       </c>
       <c r="AW126">
         <v>5.6</v>
       </c>
       <c r="AX126">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="AY126">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AZ126">
-        <v>4.9</v>
+        <v>19</v>
       </c>
       <c r="BA126">
         <v>5.7</v>
@@ -32007,19 +32007,19 @@
         <v>1000</v>
       </c>
       <c r="BI126">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BJ126">
         <v>15.5</v>
       </c>
       <c r="BK126">
-        <v>6.8</v>
+        <v>1.55</v>
       </c>
       <c r="BL126">
         <v>1000</v>
       </c>
       <c r="BM126">
-        <v>21</v>
+        <v>1.72</v>
       </c>
       <c r="BN126">
         <v>6.6</v>
@@ -32031,13 +32031,13 @@
         <v>26</v>
       </c>
       <c r="BQ126">
-        <v>11</v>
+        <v>1.62</v>
       </c>
       <c r="BR126">
         <v>1000</v>
       </c>
       <c r="BS126">
-        <v>21</v>
+        <v>1.67</v>
       </c>
       <c r="BT126">
         <v>10</v>
@@ -32049,19 +32049,19 @@
         <v>1000</v>
       </c>
       <c r="BW126">
-        <v>21</v>
+        <v>1.67</v>
       </c>
       <c r="BX126">
         <v>1000</v>
       </c>
       <c r="BY126">
-        <v>21</v>
+        <v>1.69</v>
       </c>
       <c r="BZ126">
         <v>1000</v>
       </c>
       <c r="CA126">
-        <v>21</v>
+        <v>1.67</v>
       </c>
       <c r="CB126" t="s">
         <v>408</v>
